--- a/2021 Rookies/2021_Rookie_Profiles.xlsx
+++ b/2021 Rookies/2021_Rookie_Profiles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bborh\OneDrive - The Ohio State University\Fantasy Football\Rookie Ranking\2021 Rookies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bborh\Documents\Fantasy Football\Rookie Ranking\2021 Rookies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633B29A0-DA6B-4D73-B8D3-6077EF994F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B832EABB-D95D-4A1C-A7DB-63C6E507A081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10148" yWindow="-98" windowWidth="19395" windowHeight="11596" activeTab="2" xr2:uid="{F33ABD24-CD8E-4442-8341-CD99FC2CEFD0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{F33ABD24-CD8E-4442-8341-CD99FC2CEFD0}"/>
   </bookViews>
   <sheets>
     <sheet name="Quarterbacks" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="190">
   <si>
     <t>Player</t>
   </si>
@@ -266,9 +266,6 @@
     <t>Jaylen Waddle</t>
   </si>
   <si>
-    <t>Terrace Marshall Jr.</t>
-  </si>
-  <si>
     <t>Rashod Bateman</t>
   </si>
   <si>
@@ -596,7 +593,19 @@
     <t>FPPS</t>
   </si>
   <si>
-    <t>PFPS</t>
+    <t>College Games</t>
+  </si>
+  <si>
+    <t>Rec.Yds_Game</t>
+  </si>
+  <si>
+    <t>Col_FPPG</t>
+  </si>
+  <si>
+    <t>Draft Day</t>
+  </si>
+  <si>
+    <t>Terrace Marshall</t>
   </si>
 </sst>
 </file>
@@ -690,7 +699,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="139">
+  <dxfs count="137">
     <dxf>
       <numFmt numFmtId="165" formatCode="0.000"/>
       <fill>
@@ -980,47 +989,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1063,6 +1031,15 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <fill>
         <patternFill patternType="solid">
@@ -1104,62 +1081,80 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1917,42 +1912,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CCBBC82E-97E8-4F65-A868-C50A5B6BD08A}" name="Table5" displayName="Table5" ref="A1:AC11" totalsRowShown="0" headerRowDxfId="138" dataDxfId="136" headerRowBorderDxfId="137" tableBorderDxfId="135">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CCBBC82E-97E8-4F65-A868-C50A5B6BD08A}" name="Table5" displayName="Table5" ref="A1:AC11" totalsRowShown="0" headerRowDxfId="136" dataDxfId="134" headerRowBorderDxfId="135" tableBorderDxfId="133">
   <autoFilter ref="A1:AC11" xr:uid="{CCBBC82E-97E8-4F65-A868-C50A5B6BD08A}"/>
   <tableColumns count="29">
-    <tableColumn id="1" xr3:uid="{78ED47E8-61D1-4B67-B879-5C645F1E7020}" name="Player" dataDxfId="134"/>
-    <tableColumn id="2" xr3:uid="{5AE33E4E-0DD5-4A1C-9639-44FC88CD21FD}" name="School" dataDxfId="133"/>
-    <tableColumn id="3" xr3:uid="{001198E4-1591-4ACA-BF10-BB5FC35339B3}" name="Pick.No" dataDxfId="132"/>
-    <tableColumn id="4" xr3:uid="{F5760842-A992-4BBC-A092-3F006831129F}" name="Team" dataDxfId="131"/>
-    <tableColumn id="5" xr3:uid="{0A31AA79-D62D-45CE-B6A4-59F2A9CB2C18}" name="College.Games" dataDxfId="130"/>
-    <tableColumn id="8" xr3:uid="{09FF3238-842E-430C-942B-13F80F06F529}" name="Completions" dataDxfId="129"/>
-    <tableColumn id="9" xr3:uid="{E7589D07-9FE0-4B5D-B7EC-71E574C39D4F}" name="Pass.Atts" dataDxfId="128"/>
-    <tableColumn id="10" xr3:uid="{3E974C66-D233-456A-B191-AC036789E562}" name="CMP%" dataDxfId="127"/>
-    <tableColumn id="11" xr3:uid="{B8B33B47-2AA2-4984-A725-DD38DD5C3D28}" name="Pass.Yds" dataDxfId="126"/>
-    <tableColumn id="12" xr3:uid="{B2A8C042-ED5B-4462-9BAF-27F10DCB64A5}" name="Pass.YPA" dataDxfId="125"/>
-    <tableColumn id="13" xr3:uid="{F44C2E61-2D30-4325-8734-AC3C74BC5552}" name="Pass.TD" dataDxfId="124"/>
-    <tableColumn id="14" xr3:uid="{6C262663-4D49-43D0-A31A-580F2E710BE9}" name="TD%" dataDxfId="123"/>
-    <tableColumn id="15" xr3:uid="{8989E0C1-FA7B-46D2-9F17-60F56C91A3DD}" name="INT" dataDxfId="122"/>
-    <tableColumn id="16" xr3:uid="{88842709-4551-476B-B9A1-FF87BD7A8DEF}" name="QBR" dataDxfId="121"/>
-    <tableColumn id="17" xr3:uid="{BE53280A-D339-49CA-B27E-6906530F2E53}" name="Rush.Att" dataDxfId="120"/>
-    <tableColumn id="18" xr3:uid="{AEF3B7CE-0607-480E-9B16-171496383F21}" name="Rush.Yds" dataDxfId="119"/>
-    <tableColumn id="19" xr3:uid="{439D9C80-5A4B-40B7-8D8B-96D9E76279B9}" name="Rush.YPA" dataDxfId="118"/>
-    <tableColumn id="20" xr3:uid="{38B82DC5-32B2-4F53-8EF0-0275A0146F2E}" name="Rush.TD" dataDxfId="117"/>
-    <tableColumn id="21" xr3:uid="{9AC19743-3A35-4AE4-B9F4-856D473FCEF0}" name="Fumbles" dataDxfId="116"/>
-    <tableColumn id="22" xr3:uid="{0D927F0E-AC67-4A9B-94DC-20FA494D3F51}" name="DOB" dataDxfId="115"/>
-    <tableColumn id="23" xr3:uid="{1FA9F995-6107-47B0-84DA-BA1E7E521D36}" name="Age" dataDxfId="114">
+    <tableColumn id="1" xr3:uid="{78ED47E8-61D1-4B67-B879-5C645F1E7020}" name="Player" dataDxfId="132"/>
+    <tableColumn id="2" xr3:uid="{5AE33E4E-0DD5-4A1C-9639-44FC88CD21FD}" name="School" dataDxfId="131"/>
+    <tableColumn id="3" xr3:uid="{001198E4-1591-4ACA-BF10-BB5FC35339B3}" name="Pick.No" dataDxfId="130"/>
+    <tableColumn id="4" xr3:uid="{F5760842-A992-4BBC-A092-3F006831129F}" name="Team" dataDxfId="129"/>
+    <tableColumn id="5" xr3:uid="{0A31AA79-D62D-45CE-B6A4-59F2A9CB2C18}" name="College.Games" dataDxfId="128"/>
+    <tableColumn id="8" xr3:uid="{09FF3238-842E-430C-942B-13F80F06F529}" name="Completions" dataDxfId="127"/>
+    <tableColumn id="9" xr3:uid="{E7589D07-9FE0-4B5D-B7EC-71E574C39D4F}" name="Pass.Atts" dataDxfId="126"/>
+    <tableColumn id="10" xr3:uid="{3E974C66-D233-456A-B191-AC036789E562}" name="CMP%" dataDxfId="125"/>
+    <tableColumn id="11" xr3:uid="{B8B33B47-2AA2-4984-A725-DD38DD5C3D28}" name="Pass.Yds" dataDxfId="124"/>
+    <tableColumn id="12" xr3:uid="{B2A8C042-ED5B-4462-9BAF-27F10DCB64A5}" name="Pass.YPA" dataDxfId="123"/>
+    <tableColumn id="13" xr3:uid="{F44C2E61-2D30-4325-8734-AC3C74BC5552}" name="Pass.TD" dataDxfId="122"/>
+    <tableColumn id="14" xr3:uid="{6C262663-4D49-43D0-A31A-580F2E710BE9}" name="TD%" dataDxfId="121"/>
+    <tableColumn id="15" xr3:uid="{8989E0C1-FA7B-46D2-9F17-60F56C91A3DD}" name="INT" dataDxfId="120"/>
+    <tableColumn id="16" xr3:uid="{88842709-4551-476B-B9A1-FF87BD7A8DEF}" name="QBR" dataDxfId="119"/>
+    <tableColumn id="17" xr3:uid="{BE53280A-D339-49CA-B27E-6906530F2E53}" name="Rush.Att" dataDxfId="118"/>
+    <tableColumn id="18" xr3:uid="{AEF3B7CE-0607-480E-9B16-171496383F21}" name="Rush.Yds" dataDxfId="117"/>
+    <tableColumn id="19" xr3:uid="{439D9C80-5A4B-40B7-8D8B-96D9E76279B9}" name="Rush.YPA" dataDxfId="116"/>
+    <tableColumn id="20" xr3:uid="{38B82DC5-32B2-4F53-8EF0-0275A0146F2E}" name="Rush.TD" dataDxfId="115"/>
+    <tableColumn id="21" xr3:uid="{9AC19743-3A35-4AE4-B9F4-856D473FCEF0}" name="Fumbles" dataDxfId="114"/>
+    <tableColumn id="22" xr3:uid="{0D927F0E-AC67-4A9B-94DC-20FA494D3F51}" name="DOB" dataDxfId="113"/>
+    <tableColumn id="23" xr3:uid="{1FA9F995-6107-47B0-84DA-BA1E7E521D36}" name="Age" dataDxfId="112">
       <calculatedColumnFormula>(TODAY()-T2)/365</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{4FE78187-416D-4A58-8E3E-B37B75D2A7E8}" name="Height (in.)" dataDxfId="113"/>
-    <tableColumn id="25" xr3:uid="{0E6558F1-2BFF-453C-8532-2DE1A53EB2DA}" name="Weight" dataDxfId="112"/>
-    <tableColumn id="26" xr3:uid="{64DF9291-902B-4845-9549-A2D14CEAF7CB}" name="Breakout.Age" dataDxfId="111"/>
-    <tableColumn id="29" xr3:uid="{F798CC4F-D771-4C4C-A830-AE00F42A48E8}" name="NFL.Games" dataDxfId="110"/>
-    <tableColumn id="6" xr3:uid="{611F914C-1E1A-4C05-97A1-F177B50675B8}" name="Snaps" dataDxfId="109"/>
-    <tableColumn id="27" xr3:uid="{B0634BC4-C59C-4CF8-AC64-6ED1416F40A4}" name="FP" dataDxfId="108"/>
-    <tableColumn id="7" xr3:uid="{D035CDE6-7518-47C8-9BA7-FC8E0B1AE278}" name="FPPG" dataDxfId="107">
+    <tableColumn id="24" xr3:uid="{4FE78187-416D-4A58-8E3E-B37B75D2A7E8}" name="Height (in.)" dataDxfId="111"/>
+    <tableColumn id="25" xr3:uid="{0E6558F1-2BFF-453C-8532-2DE1A53EB2DA}" name="Weight" dataDxfId="110"/>
+    <tableColumn id="26" xr3:uid="{64DF9291-902B-4845-9549-A2D14CEAF7CB}" name="Breakout.Age" dataDxfId="109"/>
+    <tableColumn id="29" xr3:uid="{F798CC4F-D771-4C4C-A830-AE00F42A48E8}" name="NFL.Games" dataDxfId="108"/>
+    <tableColumn id="6" xr3:uid="{611F914C-1E1A-4C05-97A1-F177B50675B8}" name="Snaps" dataDxfId="107"/>
+    <tableColumn id="27" xr3:uid="{B0634BC4-C59C-4CF8-AC64-6ED1416F40A4}" name="FP" dataDxfId="106"/>
+    <tableColumn id="7" xr3:uid="{D035CDE6-7518-47C8-9BA7-FC8E0B1AE278}" name="FPPG" dataDxfId="105">
       <calculatedColumnFormula>AA2/Y2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{3E7AF11F-4C73-4E7E-B72F-2509C9709209}" name="FPPS" dataDxfId="106">
+    <tableColumn id="28" xr3:uid="{3E7AF11F-4C73-4E7E-B72F-2509C9709209}" name="FPPS" dataDxfId="104">
       <calculatedColumnFormula>AA2/Z2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1961,45 +1956,45 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0D793E08-A661-449F-BF53-7507CC40DACE}" name="Table6" displayName="Table6" ref="A1:AH20" totalsRowShown="0" headerRowDxfId="105" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0D793E08-A661-449F-BF53-7507CC40DACE}" name="Table6" displayName="Table6" ref="A1:AH20" totalsRowShown="0" headerRowDxfId="103" dataDxfId="101" headerRowBorderDxfId="102" tableBorderDxfId="100">
   <autoFilter ref="A1:AH20" xr:uid="{0D793E08-A661-449F-BF53-7507CC40DACE}"/>
   <tableColumns count="34">
-    <tableColumn id="1" xr3:uid="{E1F5453A-1532-4E4E-BB09-26D1C6B7F0EA}" name="Player" dataDxfId="101"/>
-    <tableColumn id="2" xr3:uid="{BC3071E0-8652-4B28-BFB9-F5C6C99B506D}" name="School" dataDxfId="100"/>
-    <tableColumn id="3" xr3:uid="{37544652-94B4-47E2-8152-1013E8BCA200}" name="Pick.No" dataDxfId="99"/>
-    <tableColumn id="4" xr3:uid="{C1312BF3-AE6E-4021-BCE8-1A4777C8D6FE}" name="Team" dataDxfId="98"/>
-    <tableColumn id="5" xr3:uid="{2871F1D4-CA60-45B2-9813-697DC8FBFB14}" name="College.Games" dataDxfId="97"/>
-    <tableColumn id="6" xr3:uid="{507905F6-2B12-4E64-A937-768AE4D1D29A}" name="Rush.Atts" dataDxfId="96"/>
-    <tableColumn id="7" xr3:uid="{F65F7DBE-8CA5-49D0-952F-246DBCCA08F8}" name="Rush.Yds" dataDxfId="95"/>
-    <tableColumn id="8" xr3:uid="{413C55E4-085A-4ED7-87E0-763F01E8543A}" name="Rush.YPA" dataDxfId="94"/>
-    <tableColumn id="9" xr3:uid="{63A76FEE-AFC1-4B37-A80E-57F3593BF225}" name="Rush.Long" dataDxfId="93"/>
-    <tableColumn id="10" xr3:uid="{7D4CF15E-5678-4C24-823A-46C41BC322E2}" name="Rush.TDs" dataDxfId="92"/>
-    <tableColumn id="11" xr3:uid="{69CE1CD1-5838-4B69-BD37-DE6C2A6DE268}" name="Fumbles" dataDxfId="91"/>
-    <tableColumn id="12" xr3:uid="{04471CD2-F145-4218-A079-8AA8E907105E}" name="Receptions" dataDxfId="90"/>
-    <tableColumn id="13" xr3:uid="{F493EDE9-E16D-4968-8EB8-053060ACDFC5}" name="Rec.Yds" dataDxfId="89"/>
-    <tableColumn id="14" xr3:uid="{E4DDC732-97A8-494E-B05F-1EFABD5D7379}" name="YPC" dataDxfId="88"/>
-    <tableColumn id="15" xr3:uid="{7D471220-0F21-49A0-BFB2-5B574793D952}" name="Rec.TDs" dataDxfId="87"/>
-    <tableColumn id="16" xr3:uid="{B043531F-666D-46EF-A5A2-6F6CE6AA5F99}" name="Rush.Att.Per" dataDxfId="86"/>
-    <tableColumn id="17" xr3:uid="{65077B4B-422F-4339-B16D-A2EDE486D326}" name="Rush.Yds.Per" dataDxfId="85"/>
-    <tableColumn id="18" xr3:uid="{15F15F4C-807C-4A55-AE23-EE90A331ACEB}" name="Rec.Per" dataDxfId="84"/>
-    <tableColumn id="19" xr3:uid="{AF0D7B3D-703F-4ACD-B1C6-5CC397EB46D0}" name="Rec.Yds.Per" dataDxfId="83"/>
-    <tableColumn id="20" xr3:uid="{21FAFBAC-F35D-4B1B-BCCA-E4B65D5DC8E2}" name="Total.Yds.Per" dataDxfId="82"/>
-    <tableColumn id="21" xr3:uid="{9D15F7CE-6713-473B-9626-C6FCA202F92C}" name="Total.Tch.Per" dataDxfId="81"/>
-    <tableColumn id="22" xr3:uid="{01BB5B3A-532A-40AC-A2C3-DCFA06B2CF74}" name="Dom.Per" dataDxfId="80"/>
-    <tableColumn id="23" xr3:uid="{EDDCFA3F-09B5-400D-AFD9-868439BBA828}" name="Vac.Car" dataDxfId="79"/>
-    <tableColumn id="24" xr3:uid="{B6BAF15E-7AA5-4644-AB7E-25FCE7EA9264}" name="Vac.Tar" dataDxfId="78"/>
-    <tableColumn id="25" xr3:uid="{07239024-473B-4D42-8A20-FAC91496D6E5}" name="DOB" dataDxfId="77"/>
-    <tableColumn id="26" xr3:uid="{FD347E03-BAA2-4A50-8056-A19203058D02}" name="Age" dataDxfId="76">
+    <tableColumn id="1" xr3:uid="{E1F5453A-1532-4E4E-BB09-26D1C6B7F0EA}" name="Player" dataDxfId="99"/>
+    <tableColumn id="2" xr3:uid="{BC3071E0-8652-4B28-BFB9-F5C6C99B506D}" name="School" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{37544652-94B4-47E2-8152-1013E8BCA200}" name="Pick.No" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{C1312BF3-AE6E-4021-BCE8-1A4777C8D6FE}" name="Team" dataDxfId="96"/>
+    <tableColumn id="5" xr3:uid="{2871F1D4-CA60-45B2-9813-697DC8FBFB14}" name="College.Games" dataDxfId="95"/>
+    <tableColumn id="6" xr3:uid="{507905F6-2B12-4E64-A937-768AE4D1D29A}" name="Rush.Atts" dataDxfId="94"/>
+    <tableColumn id="7" xr3:uid="{F65F7DBE-8CA5-49D0-952F-246DBCCA08F8}" name="Rush.Yds" dataDxfId="93"/>
+    <tableColumn id="8" xr3:uid="{413C55E4-085A-4ED7-87E0-763F01E8543A}" name="Rush.YPA" dataDxfId="92"/>
+    <tableColumn id="9" xr3:uid="{63A76FEE-AFC1-4B37-A80E-57F3593BF225}" name="Rush.Long" dataDxfId="91"/>
+    <tableColumn id="10" xr3:uid="{7D4CF15E-5678-4C24-823A-46C41BC322E2}" name="Rush.TDs" dataDxfId="90"/>
+    <tableColumn id="11" xr3:uid="{69CE1CD1-5838-4B69-BD37-DE6C2A6DE268}" name="Fumbles" dataDxfId="89"/>
+    <tableColumn id="12" xr3:uid="{04471CD2-F145-4218-A079-8AA8E907105E}" name="Receptions" dataDxfId="88"/>
+    <tableColumn id="13" xr3:uid="{F493EDE9-E16D-4968-8EB8-053060ACDFC5}" name="Rec.Yds" dataDxfId="87"/>
+    <tableColumn id="14" xr3:uid="{E4DDC732-97A8-494E-B05F-1EFABD5D7379}" name="YPC" dataDxfId="86"/>
+    <tableColumn id="15" xr3:uid="{7D471220-0F21-49A0-BFB2-5B574793D952}" name="Rec.TDs" dataDxfId="85"/>
+    <tableColumn id="16" xr3:uid="{B043531F-666D-46EF-A5A2-6F6CE6AA5F99}" name="Rush.Att.Per" dataDxfId="84"/>
+    <tableColumn id="17" xr3:uid="{65077B4B-422F-4339-B16D-A2EDE486D326}" name="Rush.Yds.Per" dataDxfId="83"/>
+    <tableColumn id="18" xr3:uid="{15F15F4C-807C-4A55-AE23-EE90A331ACEB}" name="Rec.Per" dataDxfId="82"/>
+    <tableColumn id="19" xr3:uid="{AF0D7B3D-703F-4ACD-B1C6-5CC397EB46D0}" name="Rec.Yds.Per" dataDxfId="81"/>
+    <tableColumn id="20" xr3:uid="{21FAFBAC-F35D-4B1B-BCCA-E4B65D5DC8E2}" name="Total.Yds.Per" dataDxfId="80"/>
+    <tableColumn id="21" xr3:uid="{9D15F7CE-6713-473B-9626-C6FCA202F92C}" name="Total.Tch.Per" dataDxfId="79"/>
+    <tableColumn id="22" xr3:uid="{01BB5B3A-532A-40AC-A2C3-DCFA06B2CF74}" name="Dom.Per" dataDxfId="78"/>
+    <tableColumn id="23" xr3:uid="{EDDCFA3F-09B5-400D-AFD9-868439BBA828}" name="Vac.Car" dataDxfId="77"/>
+    <tableColumn id="24" xr3:uid="{B6BAF15E-7AA5-4644-AB7E-25FCE7EA9264}" name="Vac.Tar" dataDxfId="76"/>
+    <tableColumn id="25" xr3:uid="{07239024-473B-4D42-8A20-FAC91496D6E5}" name="DOB" dataDxfId="75"/>
+    <tableColumn id="26" xr3:uid="{FD347E03-BAA2-4A50-8056-A19203058D02}" name="Age" dataDxfId="74">
       <calculatedColumnFormula>(TODAY()-Y2)/365</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{321B13F2-3033-414D-8BF7-06C35E267DB5}" name="Height (in.)" dataDxfId="75"/>
-    <tableColumn id="28" xr3:uid="{5E6116FD-F406-43D9-B9D5-D3B74CA852D0}" name="Weight" dataDxfId="74"/>
-    <tableColumn id="29" xr3:uid="{1B1F2C51-5439-4E97-AF08-696A5398DF6B}" name="Breakout Age" dataDxfId="73"/>
-    <tableColumn id="30" xr3:uid="{722FED33-7DC8-496F-9D37-A296529DB86E}" name="NFL.Games" dataDxfId="72"/>
-    <tableColumn id="34" xr3:uid="{A42C6EC6-EB55-44AB-97C2-76FD15497EB0}" name="Snaps" dataDxfId="71"/>
-    <tableColumn id="31" xr3:uid="{D551B6C1-65D6-4AAD-B8FC-F876E1A34334}" name="FP" dataDxfId="70"/>
-    <tableColumn id="33" xr3:uid="{9091F112-402F-4CFE-BE75-FF603EF638C7}" name="FPPG" dataDxfId="69"/>
-    <tableColumn id="32" xr3:uid="{6E8B14C7-9411-43ED-8B04-128E8B30496A}" name="FPPS" dataDxfId="68">
+    <tableColumn id="27" xr3:uid="{321B13F2-3033-414D-8BF7-06C35E267DB5}" name="Height (in.)" dataDxfId="73"/>
+    <tableColumn id="28" xr3:uid="{5E6116FD-F406-43D9-B9D5-D3B74CA852D0}" name="Weight" dataDxfId="72"/>
+    <tableColumn id="29" xr3:uid="{1B1F2C51-5439-4E97-AF08-696A5398DF6B}" name="Breakout Age" dataDxfId="71"/>
+    <tableColumn id="30" xr3:uid="{722FED33-7DC8-496F-9D37-A296529DB86E}" name="NFL.Games" dataDxfId="70"/>
+    <tableColumn id="34" xr3:uid="{A42C6EC6-EB55-44AB-97C2-76FD15497EB0}" name="Snaps" dataDxfId="69"/>
+    <tableColumn id="31" xr3:uid="{D551B6C1-65D6-4AAD-B8FC-F876E1A34334}" name="FP" dataDxfId="68"/>
+    <tableColumn id="33" xr3:uid="{9091F112-402F-4CFE-BE75-FF603EF638C7}" name="FPPG" dataDxfId="67"/>
+    <tableColumn id="32" xr3:uid="{6E8B14C7-9411-43ED-8B04-128E8B30496A}" name="FPPS" dataDxfId="66">
       <calculatedColumnFormula>Table6[[#This Row],[FP]]/Table6[[#This Row],[Snaps]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2008,48 +2003,46 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C143BBF7-9B13-4730-B62F-B39632C66D4C}" name="Table7" displayName="Table7" ref="A1:AD28" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64">
-  <autoFilter ref="A1:AD28" xr:uid="{C143BBF7-9B13-4730-B62F-B39632C66D4C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD28">
-    <sortCondition ref="D2:D28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C143BBF7-9B13-4730-B62F-B39632C66D4C}" name="Table7" displayName="Table7" ref="A1:AB28" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" tableBorderDxfId="62">
+  <autoFilter ref="A1:AB28" xr:uid="{C143BBF7-9B13-4730-B62F-B39632C66D4C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB28">
+    <sortCondition ref="C1:C28"/>
   </sortState>
-  <tableColumns count="30">
-    <tableColumn id="1" xr3:uid="{D569FE3B-A4A6-41A8-B81D-EB5B3809FD92}" name="Player" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{21D20578-4206-48BA-8924-4F84360E39C4}" name="School" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{72FBC9C5-E592-4C0B-B6EE-785347390052}" name="Pick.No" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{3957745F-0BCA-4F43-BEE1-A7CD9C833ADB}" name="Team" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{F76779C3-2526-416B-90D9-65A56933560C}" name="College.Games" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{43D3E475-9408-47DF-B0F0-8891FC5A408B}" name="Receptions" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{389112F9-0C76-43A9-89AC-AC91F69B7249}" name="Rec.Yds" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{0D2B7768-46FD-4644-9546-664214506DB0}" name="YPC" dataDxfId="56"/>
-    <tableColumn id="9" xr3:uid="{2793822F-F82E-4AF4-88C4-E53FC1A1326A}" name="Rec.Long" dataDxfId="55"/>
-    <tableColumn id="10" xr3:uid="{3BA03D7B-0D5E-404E-9CE1-962522264CCE}" name="Rec.TDs" dataDxfId="54"/>
-    <tableColumn id="11" xr3:uid="{1BBAEF7D-6135-4404-8D68-9D5F47B6AC6E}" name="Rush.Atts" dataDxfId="53"/>
-    <tableColumn id="12" xr3:uid="{D31B4DFA-C268-4839-BE6E-79C5B45E8C02}" name="Rush.Yds" dataDxfId="52"/>
-    <tableColumn id="13" xr3:uid="{F564E615-979A-4E22-982A-3DADA7E531EE}" name="Rush.YPA" dataDxfId="51"/>
-    <tableColumn id="14" xr3:uid="{76D1B38A-FB5C-4A2F-A574-2ECF63539C55}" name="Rush.TDs" dataDxfId="50"/>
-    <tableColumn id="15" xr3:uid="{7C10AB96-DCB5-4A23-9849-43F67F55688D}" name="Fumbles" dataDxfId="49"/>
-    <tableColumn id="16" xr3:uid="{A022B30D-C20F-40B2-8F66-2F9501310FCD}" name="Rec.Per" dataDxfId="48"/>
-    <tableColumn id="17" xr3:uid="{C9114F99-FC26-495E-9DB7-7651704FFD92}" name="Rec.Yds.Per" dataDxfId="47"/>
-    <tableColumn id="18" xr3:uid="{08E3A0CC-F9BE-48BB-B891-90E2D27726F8}" name="Rec.TDs.Per" dataDxfId="46"/>
-    <tableColumn id="19" xr3:uid="{F26329C6-0298-49CD-BF6F-986F7E681615}" name="Dom.Per" dataDxfId="45"/>
-    <tableColumn id="20" xr3:uid="{E034DE9B-9D19-4AE6-861C-51D7FF6B94A6}" name="Vac.Tar" dataDxfId="44"/>
-    <tableColumn id="21" xr3:uid="{4B90E66F-9B33-493A-9293-0906050FCAA1}" name="DOB" dataDxfId="43"/>
-    <tableColumn id="22" xr3:uid="{88BAC108-E13F-4476-ACB4-8FE792CA9EF3}" name="Age" dataDxfId="42">
-      <calculatedColumnFormula>(TODAY()-U2)/365</calculatedColumnFormula>
+  <tableColumns count="28">
+    <tableColumn id="1" xr3:uid="{D569FE3B-A4A6-41A8-B81D-EB5B3809FD92}" name="Player" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{21D20578-4206-48BA-8924-4F84360E39C4}" name="School" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{72FBC9C5-E592-4C0B-B6EE-785347390052}" name="Pick.No" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{3957745F-0BCA-4F43-BEE1-A7CD9C833ADB}" name="Team" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{F76779C3-2526-416B-90D9-65A56933560C}" name="College Games" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{43D3E475-9408-47DF-B0F0-8891FC5A408B}" name="Receptions" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{389112F9-0C76-43A9-89AC-AC91F69B7249}" name="Rec.Yds" dataDxfId="55"/>
+    <tableColumn id="32" xr3:uid="{CA28044E-549B-4148-9D9F-AFC033D2AC43}" name="Rec.Yds_Game" dataDxfId="54">
+      <calculatedColumnFormula>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{5DE0478B-F9E2-43B6-823C-CADCB58F453B}" name="Height (in.)" dataDxfId="41"/>
-    <tableColumn id="24" xr3:uid="{5C591721-F463-4BE3-B5CD-2ADE727F4D2E}" name="Weight" dataDxfId="40"/>
-    <tableColumn id="25" xr3:uid="{6374748A-CF87-47D6-8E27-139DD35A5EB7}" name="Breakout Age" dataDxfId="39"/>
-    <tableColumn id="26" xr3:uid="{9DFFFAD7-5C99-447F-89D3-643F7CA43F20}" name="NFL.Games" dataDxfId="38"/>
-    <tableColumn id="29" xr3:uid="{FE5BC6D5-FAB2-4ED0-8CC4-87C0A0A6F0BF}" name="Snaps" dataDxfId="37"/>
-    <tableColumn id="27" xr3:uid="{2452693D-1BCE-4DBB-A280-39EF147F73C1}" name="FP" dataDxfId="36"/>
-    <tableColumn id="30" xr3:uid="{46F595D3-F789-4B1A-A248-4DE082BC5A8E}" name="FPPG" dataDxfId="35">
-      <calculatedColumnFormula>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</calculatedColumnFormula>
+    <tableColumn id="8" xr3:uid="{0D2B7768-46FD-4644-9546-664214506DB0}" name="YPC" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{2793822F-F82E-4AF4-88C4-E53FC1A1326A}" name="Rec.Long" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{3BA03D7B-0D5E-404E-9CE1-962522264CCE}" name="Rec.TDs" dataDxfId="51"/>
+    <tableColumn id="11" xr3:uid="{1BBAEF7D-6135-4404-8D68-9D5F47B6AC6E}" name="Rush.Atts" dataDxfId="50"/>
+    <tableColumn id="12" xr3:uid="{D31B4DFA-C268-4839-BE6E-79C5B45E8C02}" name="Rush.Yds" dataDxfId="49"/>
+    <tableColumn id="13" xr3:uid="{F564E615-979A-4E22-982A-3DADA7E531EE}" name="Rush.YPA" dataDxfId="48"/>
+    <tableColumn id="14" xr3:uid="{76D1B38A-FB5C-4A2F-A574-2ECF63539C55}" name="Rush.TDs" dataDxfId="47"/>
+    <tableColumn id="15" xr3:uid="{7C10AB96-DCB5-4A23-9849-43F67F55688D}" name="Fumbles" dataDxfId="46"/>
+    <tableColumn id="33" xr3:uid="{2FF03BBF-CDCE-4257-8BB8-1206B241CEC0}" name="Col_FPPG" dataDxfId="45">
+      <calculatedColumnFormula>(F2*0.5+G2/10+K2*6+M2/10+O2*6-P2*2)/E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{D3088F8A-7213-4669-BC22-3C2ED9C7D804}" name="PFPS" dataDxfId="34">
-      <calculatedColumnFormula>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</calculatedColumnFormula>
+    <tableColumn id="16" xr3:uid="{A022B30D-C20F-40B2-8F66-2F9501310FCD}" name="Rec.Per" dataDxfId="44"/>
+    <tableColumn id="17" xr3:uid="{C9114F99-FC26-495E-9DB7-7651704FFD92}" name="Rec.Yds.Per" dataDxfId="43"/>
+    <tableColumn id="18" xr3:uid="{08E3A0CC-F9BE-48BB-B891-90E2D27726F8}" name="Rec.TDs.Per" dataDxfId="42"/>
+    <tableColumn id="19" xr3:uid="{F26329C6-0298-49CD-BF6F-986F7E681615}" name="Dom.Per" dataDxfId="41"/>
+    <tableColumn id="20" xr3:uid="{E034DE9B-9D19-4AE6-861C-51D7FF6B94A6}" name="Vac.Tar" dataDxfId="40"/>
+    <tableColumn id="21" xr3:uid="{4B90E66F-9B33-493A-9293-0906050FCAA1}" name="DOB" dataDxfId="39"/>
+    <tableColumn id="34" xr3:uid="{E35AB84D-67EF-4D2F-BBA9-F1C1F5E705AB}" name="Draft Day" dataDxfId="38"/>
+    <tableColumn id="22" xr3:uid="{88BAC108-E13F-4476-ACB4-8FE792CA9EF3}" name="Age" dataDxfId="37">
+      <calculatedColumnFormula>(X2-W2)/365</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="23" xr3:uid="{5DE0478B-F9E2-43B6-823C-CADCB58F453B}" name="Height (in.)" dataDxfId="36"/>
+    <tableColumn id="24" xr3:uid="{5C591721-F463-4BE3-B5CD-2ADE727F4D2E}" name="Weight" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{6374748A-CF87-47D6-8E27-139DD35A5EB7}" name="Breakout Age" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2440,19 +2433,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>120</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>2</v>
@@ -2491,7 +2484,7 @@
         <v>13</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U1" s="11" t="s">
         <v>14</v>
@@ -2506,19 +2499,19 @@
         <v>17</v>
       </c>
       <c r="Y1" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z1" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AA1" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB1" s="11" t="s">
         <v>18</v>
       </c>
       <c r="AC1" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
@@ -2532,7 +2525,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E2" s="1">
         <v>10</v>
@@ -2584,7 +2577,7 @@
       </c>
       <c r="U2" s="6">
         <f ca="1">(TODAY()-T2)/365</f>
-        <v>22.536986301369861</v>
+        <v>24.583561643835615</v>
       </c>
       <c r="V2" s="3">
         <f>6*12+6</f>
@@ -2625,7 +2618,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E3" s="1">
         <v>12</v>
@@ -2677,7 +2670,7 @@
       </c>
       <c r="U3" s="6">
         <f ca="1">(TODAY()-T3)/365</f>
-        <v>22.712328767123289</v>
+        <v>24.758904109589039</v>
       </c>
       <c r="V3" s="3">
         <v>75</v>
@@ -2717,7 +2710,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E4" s="1">
         <v>16</v>
@@ -2769,7 +2762,7 @@
       </c>
       <c r="U4" s="6">
         <f t="shared" ref="U4:U11" ca="1" si="2">(TODAY()-T4)/365</f>
-        <v>21.945205479452056</v>
+        <v>23.991780821917807</v>
       </c>
       <c r="V4" s="3">
         <v>76</v>
@@ -2809,7 +2802,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="1">
         <v>14</v>
@@ -2861,7 +2854,7 @@
       </c>
       <c r="U5" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>23.126027397260273</v>
+        <v>25.172602739726027</v>
       </c>
       <c r="V5" s="3">
         <f>6*12+3</f>
@@ -2902,7 +2895,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E6" s="1">
         <v>13</v>
@@ -2954,7 +2947,7 @@
       </c>
       <c r="U6" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>23.621917808219177</v>
+        <v>25.668493150684931</v>
       </c>
       <c r="V6" s="3">
         <f>6*12+3</f>
@@ -2995,7 +2988,7 @@
         <v>64</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E7" s="1">
         <v>12</v>
@@ -3047,7 +3040,7 @@
       </c>
       <c r="U7" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>24.123287671232877</v>
+        <v>26.169863013698631</v>
       </c>
       <c r="V7" s="3">
         <f>6*12+5</f>
@@ -3086,7 +3079,7 @@
         <v>66</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E8" s="1">
         <v>10</v>
@@ -3138,7 +3131,7 @@
       </c>
       <c r="U8" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>22.827397260273973</v>
+        <v>24.873972602739727</v>
       </c>
       <c r="V8" s="3">
         <f>6*12+3</f>
@@ -3169,16 +3162,16 @@
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="1">
         <v>67</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -3230,7 +3223,7 @@
       </c>
       <c r="U9" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>23.495890410958904</v>
+        <v>25.542465753424658</v>
       </c>
       <c r="V9" s="3">
         <f>6*12+4</f>
@@ -3262,7 +3255,7 @@
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>35</v>
@@ -3271,7 +3264,7 @@
         <v>133</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E10" s="1">
         <v>12</v>
@@ -3323,7 +3316,7 @@
       </c>
       <c r="U10" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>24.057534246575344</v>
+        <v>26.104109589041094</v>
       </c>
       <c r="V10" s="3">
         <f>6*12</f>
@@ -3355,7 +3348,7 @@
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>36</v>
@@ -3364,7 +3357,7 @@
         <v>218</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E11" s="1">
         <v>10</v>
@@ -3416,7 +3409,7 @@
       </c>
       <c r="U11" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>23.553424657534247</v>
+        <v>25.6</v>
       </c>
       <c r="V11" s="3">
         <f>6*12+3</f>
@@ -3533,13 +3526,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>37</v>
@@ -3572,34 +3565,34 @@
         <v>43</v>
       </c>
       <c r="P1" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q1" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="R1" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="T1" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="R1" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="T1" s="11" t="s">
+      <c r="U1" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="U1" s="11" t="s">
-        <v>146</v>
-      </c>
       <c r="V1" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="W1" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="X1" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="X1" s="11" t="s">
-        <v>180</v>
-      </c>
       <c r="Y1" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Z1" s="11" t="s">
         <v>14</v>
@@ -3614,19 +3607,19 @@
         <v>44</v>
       </c>
       <c r="AD1" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE1" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AF1" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG1" s="11" t="s">
         <v>18</v>
       </c>
       <c r="AH1" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
@@ -3640,7 +3633,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E2" s="1">
         <v>13</v>
@@ -3707,7 +3700,7 @@
       </c>
       <c r="Z2" s="8">
         <f t="shared" ref="Z2:Z11" ca="1" si="0">(TODAY()-Y2)/365</f>
-        <v>24.115068493150684</v>
+        <v>26.161643835616438</v>
       </c>
       <c r="AA2" s="7">
         <f>6*12+2</f>
@@ -3748,7 +3741,7 @@
         <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E3" s="1">
         <v>12</v>
@@ -3815,7 +3808,7 @@
       </c>
       <c r="Z3" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>23.230136986301371</v>
+        <v>25.276712328767122</v>
       </c>
       <c r="AA3" s="7">
         <f>5*12+10</f>
@@ -3854,7 +3847,7 @@
         <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E4" s="1">
         <v>11</v>
@@ -3921,7 +3914,7 @@
       </c>
       <c r="Z4" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>21.983561643835618</v>
+        <v>24.030136986301368</v>
       </c>
       <c r="AA4" s="7">
         <f>5*12+10</f>
@@ -3962,7 +3955,7 @@
         <v>88</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E5" s="1">
         <v>8</v>
@@ -4029,7 +4022,7 @@
       </c>
       <c r="Z5" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>23.219178082191782</v>
+        <v>25.265753424657536</v>
       </c>
       <c r="AA5" s="7">
         <f>6*12+1</f>
@@ -4070,7 +4063,7 @@
         <v>107</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E6" s="1">
         <v>11</v>
@@ -4137,7 +4130,7 @@
       </c>
       <c r="Z6" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>22.953424657534246</v>
+        <v>25</v>
       </c>
       <c r="AA6" s="7">
         <f>5*12+8</f>
@@ -4178,7 +4171,7 @@
         <v>120</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
@@ -4245,7 +4238,7 @@
       </c>
       <c r="Z7" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>24.153424657534245</v>
+        <v>26.2</v>
       </c>
       <c r="AA7" s="7">
         <f>6*12</f>
@@ -4286,7 +4279,7 @@
         <v>126</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E8" s="1">
         <v>13</v>
@@ -4353,7 +4346,7 @@
       </c>
       <c r="Z8" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>22.857534246575341</v>
+        <v>24.904109589041095</v>
       </c>
       <c r="AA8" s="7">
         <f>6*12</f>
@@ -4394,7 +4387,7 @@
         <v>150</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E9" s="1">
         <v>14</v>
@@ -4461,7 +4454,7 @@
       </c>
       <c r="Z9" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>23.101369863013698</v>
+        <v>25.147945205479452</v>
       </c>
       <c r="AA9" s="7">
         <f>5*12+11</f>
@@ -4502,7 +4495,7 @@
         <v>194</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E10" s="1">
         <v>14</v>
@@ -4569,7 +4562,7 @@
       </c>
       <c r="Z10" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>23.967123287671232</v>
+        <v>26.013698630136986</v>
       </c>
       <c r="AA10" s="7">
         <f>5*12+11</f>
@@ -4601,16 +4594,16 @@
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="C11" s="7">
         <v>198</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E11" s="1">
         <v>10</v>
@@ -4677,7 +4670,7 @@
       </c>
       <c r="Z11" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>24.18082191780822</v>
+        <v>26.227397260273971</v>
       </c>
       <c r="AA11" s="7">
         <f>5*12+10</f>
@@ -4687,7 +4680,7 @@
         <v>230</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AD11" s="7">
         <v>0</v>
@@ -4708,7 +4701,7 @@
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>69</v>
@@ -4717,7 +4710,7 @@
         <v>202</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E12" s="1">
         <v>11</v>
@@ -4784,7 +4777,7 @@
       </c>
       <c r="Z12" s="8">
         <f t="shared" ref="Z12:Z19" ca="1" si="1">(TODAY()-Y12)/365</f>
-        <v>24.539726027397261</v>
+        <v>26.586301369863012</v>
       </c>
       <c r="AA12" s="7">
         <f>5*12+11</f>
@@ -4816,16 +4809,16 @@
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="C13" s="7">
         <v>211</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
@@ -4892,7 +4885,7 @@
       </c>
       <c r="Z13" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>23.761643835616439</v>
+        <v>25.80821917808219</v>
       </c>
       <c r="AA13" s="7">
         <f>5*12+10</f>
@@ -4933,7 +4926,7 @@
         <v>217</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E14" s="1">
         <v>11</v>
@@ -5000,7 +4993,7 @@
       </c>
       <c r="Z14" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>23.997260273972604</v>
+        <v>26.043835616438358</v>
       </c>
       <c r="AA14" s="7">
         <f>5*12+9</f>
@@ -5032,16 +5025,16 @@
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="C15" s="7">
         <v>233</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15" s="1">
         <v>4</v>
@@ -5108,7 +5101,7 @@
       </c>
       <c r="Z15" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>24.271232876712329</v>
+        <v>26.317808219178083</v>
       </c>
       <c r="AA15" s="7">
         <f>5*12+10</f>
@@ -5118,7 +5111,7 @@
         <v>205</v>
       </c>
       <c r="AC15" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AD15" s="7">
         <v>0</v>
@@ -5148,7 +5141,7 @@
         <v>256</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E16" s="1">
         <v>13</v>
@@ -5215,7 +5208,7 @@
       </c>
       <c r="Z16" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>23.671232876712327</v>
+        <v>25.717808219178082</v>
       </c>
       <c r="AA16" s="7">
         <f>5*12+11</f>
@@ -5255,7 +5248,7 @@
         <v>257</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
@@ -5322,7 +5315,7 @@
       </c>
       <c r="Z17" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>22.010958904109589</v>
+        <v>24.057534246575344</v>
       </c>
       <c r="AA17" s="7">
         <f>5*12+10</f>
@@ -5359,10 +5352,10 @@
         <v>64</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
@@ -5429,7 +5422,7 @@
       </c>
       <c r="Z18" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>22.323287671232876</v>
+        <v>24.36986301369863</v>
       </c>
       <c r="AA18" s="7">
         <f>5*12+9</f>
@@ -5467,10 +5460,10 @@
         <v>65</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E19" s="1">
         <v>13</v>
@@ -5537,7 +5530,7 @@
       </c>
       <c r="Z19" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>22.460273972602739</v>
+        <v>24.506849315068493</v>
       </c>
       <c r="AA19" s="7">
         <f>5*12+9</f>
@@ -5573,10 +5566,10 @@
         <v>67</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E20" s="1">
         <v>12</v>
@@ -5643,7 +5636,7 @@
       </c>
       <c r="Z20" s="8">
         <f ca="1">(TODAY()-Y20)/365</f>
-        <v>23.167123287671235</v>
+        <v>25.213698630136985</v>
       </c>
       <c r="AA20" s="7">
         <f>6*12</f>
@@ -5689,43 +5682,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD2050A7-C654-44F6-95AC-D46086B394BC}">
-  <dimension ref="A1:AD30"/>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" style="3" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="3" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="3" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" style="3" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="3" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="3" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15" style="3" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="3" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="3" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="3" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="3" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="3" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="17" style="3" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" style="3" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="14.140625" style="3" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="3"/>
+    <col min="5" max="5" width="19.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="3" customWidth="1"/>
+    <col min="7" max="8" width="13.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="15" style="3" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="3" customWidth="1"/>
+    <col min="16" max="17" width="13.85546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="17" style="3" customWidth="1"/>
+    <col min="20" max="20" width="17.140625" style="3" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" style="3" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12" style="3" customWidth="1"/>
+    <col min="25" max="25" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -5733,13 +5722,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>40</v>
@@ -5748,2670 +5737,2507 @@
         <v>41</v>
       </c>
       <c r="H1" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="N1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="P1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="Q1" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="S1" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="T1" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="U1" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="S1" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="T1" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="U1" s="11" t="s">
-        <v>116</v>
-      </c>
       <c r="V1" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="X1" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="Z1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="AA1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="AB1" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="Z1" s="11" t="s">
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="3">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="1">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3">
+        <v>84</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1780</v>
+      </c>
+      <c r="H2" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>127.14285714285714</v>
+      </c>
+      <c r="I2" s="3">
+        <v>21.2</v>
+      </c>
+      <c r="J2" s="3">
+        <v>78</v>
+      </c>
+      <c r="K2" s="3">
+        <v>20</v>
+      </c>
+      <c r="L2" s="3">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3">
+        <v>5</v>
+      </c>
+      <c r="N2" s="3">
+        <v>5</v>
+      </c>
+      <c r="O2" s="3">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="4">
+        <f>(F2*0.5+G2/10+K2*6+M2/10+O2*6-P2*2)/E2</f>
+        <v>24.178571428571427</v>
+      </c>
+      <c r="R2" s="3">
+        <v>21</v>
+      </c>
+      <c r="S2" s="3">
+        <v>32</v>
+      </c>
+      <c r="T2" s="3">
+        <v>35</v>
+      </c>
+      <c r="U2" s="3">
+        <v>33</v>
+      </c>
+      <c r="V2" s="4">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="W2" s="5">
+        <v>36586</v>
+      </c>
+      <c r="X2" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y2" s="6">
+        <f>(X2-W2)/365</f>
+        <v>21.175342465753424</v>
+      </c>
+      <c r="Z2" s="3">
+        <f>6*12</f>
+        <v>72</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>208</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="1">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3">
+        <v>28</v>
+      </c>
+      <c r="G3" s="3">
+        <v>591</v>
+      </c>
+      <c r="H3" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>98.5</v>
+      </c>
+      <c r="I3" s="3">
+        <v>21.1</v>
+      </c>
+      <c r="J3" s="3">
+        <v>90</v>
+      </c>
+      <c r="K3" s="3">
+        <v>4</v>
+      </c>
+      <c r="L3" s="3">
+        <v>3</v>
+      </c>
+      <c r="M3" s="3">
+        <v>12</v>
+      </c>
+      <c r="N3" s="3">
+        <v>4</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <f t="shared" ref="Q3:Q28" si="0">(F3*0.5+G3/10+K3*6+M3/10+O3*6-P3*2)/E3</f>
+        <v>16.383333333333333</v>
+      </c>
+      <c r="R3" s="3">
+        <v>19</v>
+      </c>
+      <c r="S3" s="3">
+        <v>28</v>
+      </c>
+      <c r="T3" s="3">
+        <v>21</v>
+      </c>
+      <c r="U3" s="3">
+        <v>24</v>
+      </c>
+      <c r="V3" s="4">
+        <v>14</v>
+      </c>
+      <c r="W3" s="5">
+        <v>36093</v>
+      </c>
+      <c r="X3" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y3" s="6">
+        <f t="shared" ref="Y3:Y28" si="1">(X3-W3)/365</f>
+        <v>22.526027397260275</v>
+      </c>
+      <c r="Z3" s="3">
+        <f>5*12+10</f>
+        <v>70</v>
+      </c>
+      <c r="AA3" s="3">
         <v>182</v>
       </c>
-      <c r="AA1" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="AB1" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="AC1" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD1" s="11" t="s">
-        <v>186</v>
+      <c r="AB3" s="3">
+        <v>21.8</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E4" s="1">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3">
+        <v>117</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1856</v>
+      </c>
+      <c r="H4" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>142.76923076923077</v>
+      </c>
+      <c r="I4" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="J4" s="3">
+        <v>66</v>
+      </c>
+      <c r="K4" s="3">
+        <v>23</v>
+      </c>
+      <c r="L4" s="3">
+        <v>4</v>
+      </c>
+      <c r="M4" s="3">
+        <v>6</v>
+      </c>
+      <c r="N4" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="O4" s="3">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <f t="shared" si="0"/>
+        <v>29.900000000000002</v>
+      </c>
+      <c r="R4" s="3">
+        <v>36</v>
+      </c>
+      <c r="S4" s="3">
+        <v>40</v>
+      </c>
+      <c r="T4" s="3">
+        <v>55</v>
+      </c>
+      <c r="U4" s="3">
+        <v>47</v>
+      </c>
+      <c r="V4" s="4">
+        <v>13.3</v>
+      </c>
+      <c r="W4" s="5">
+        <v>36082</v>
+      </c>
+      <c r="X4" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y4" s="6">
+        <f t="shared" si="1"/>
+        <v>22.556164383561644</v>
+      </c>
+      <c r="Z4" s="3">
+        <f>6*12+1</f>
+        <v>73</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>175</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" s="1">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3">
+        <v>70</v>
+      </c>
+      <c r="G5" s="3">
+        <v>984</v>
+      </c>
+      <c r="H5" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>89.454545454545453</v>
+      </c>
+      <c r="I5" s="3">
+        <v>14.1</v>
+      </c>
+      <c r="J5" s="3">
+        <v>57</v>
+      </c>
+      <c r="K5" s="3">
+        <v>10</v>
+      </c>
+      <c r="L5" s="3">
+        <v>19</v>
+      </c>
+      <c r="M5" s="3">
+        <v>161</v>
+      </c>
+      <c r="N5" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="O5" s="3">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4">
+        <f t="shared" si="0"/>
+        <v>19.40909090909091</v>
+      </c>
+      <c r="R5" s="3">
+        <v>24</v>
+      </c>
+      <c r="S5" s="3">
+        <v>24</v>
+      </c>
+      <c r="T5" s="3">
+        <v>24</v>
+      </c>
+      <c r="U5" s="3">
+        <v>23</v>
+      </c>
+      <c r="V5" s="4">
+        <v>24.2</v>
+      </c>
+      <c r="W5" s="5">
+        <v>36187</v>
+      </c>
+      <c r="X5" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y5" s="6">
+        <f t="shared" si="1"/>
+        <v>22.268493150684932</v>
+      </c>
+      <c r="Z5" s="3">
+        <f>6*12</f>
+        <v>72</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>193</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="3">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="1">
+        <v>13</v>
+      </c>
+      <c r="F6" s="3">
+        <v>60</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1219</v>
+      </c>
+      <c r="H6" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>93.769230769230774</v>
+      </c>
+      <c r="I6" s="3">
+        <v>20.3</v>
+      </c>
+      <c r="J6" s="3">
+        <v>66</v>
+      </c>
+      <c r="K6" s="3">
+        <v>11</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <f t="shared" si="0"/>
+        <v>16.761538461538461</v>
+      </c>
+      <c r="R6" s="3">
+        <v>28</v>
+      </c>
+      <c r="S6" s="3">
+        <v>37</v>
+      </c>
+      <c r="T6" s="3">
+        <v>35</v>
+      </c>
+      <c r="U6" s="3">
+        <v>36</v>
+      </c>
+      <c r="V6" s="4">
+        <v>21.7</v>
+      </c>
+      <c r="W6" s="5">
+        <v>36462</v>
+      </c>
+      <c r="X6" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y6" s="6">
+        <f t="shared" si="1"/>
+        <v>21.515068493150686</v>
+      </c>
+      <c r="Z6" s="3">
+        <f>6*12+2</f>
+        <v>74</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>210</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="3">
-        <v>49</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E2" s="1">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3">
-        <v>114</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1258</v>
-      </c>
-      <c r="H2" s="3">
-        <v>11</v>
-      </c>
-      <c r="I2" s="3">
-        <v>70</v>
-      </c>
-      <c r="J2" s="3">
-        <v>12</v>
-      </c>
-      <c r="K2" s="3">
-        <v>21</v>
-      </c>
-      <c r="L2" s="3">
-        <v>213</v>
-      </c>
-      <c r="M2" s="3">
-        <v>10.1</v>
-      </c>
-      <c r="N2" s="3">
-        <v>2</v>
-      </c>
-      <c r="O2" s="3">
-        <v>2</v>
-      </c>
-      <c r="P2" s="3">
+      <c r="C7" s="3">
         <v>34</v>
       </c>
-      <c r="Q2" s="3">
-        <v>31</v>
-      </c>
-      <c r="R2" s="3">
+      <c r="D7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="1">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>86</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1193</v>
+      </c>
+      <c r="H7" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>149.125</v>
+      </c>
+      <c r="I7" s="3">
+        <v>13.9</v>
+      </c>
+      <c r="J7" s="3">
+        <v>91</v>
+      </c>
+      <c r="K7" s="3">
+        <v>8</v>
+      </c>
+      <c r="L7" s="3">
+        <v>14</v>
+      </c>
+      <c r="M7" s="3">
+        <v>64</v>
+      </c>
+      <c r="N7" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4">
+        <f t="shared" si="0"/>
+        <v>26.837500000000002</v>
+      </c>
+      <c r="R7" s="3">
+        <v>45</v>
+      </c>
+      <c r="S7" s="3">
         <v>43</v>
       </c>
-      <c r="S2" s="3">
-        <v>37</v>
-      </c>
-      <c r="T2" s="4">
-        <v>21</v>
-      </c>
-      <c r="U2" s="5">
-        <v>36686</v>
-      </c>
-      <c r="V2" s="6">
-        <f t="shared" ref="V2:V28" ca="1" si="0">(TODAY()-U2)/365</f>
-        <v>21.860273972602741</v>
-      </c>
-      <c r="W2" s="3">
+      <c r="T7" s="3">
+        <v>33</v>
+      </c>
+      <c r="U7" s="3">
+        <v>38</v>
+      </c>
+      <c r="V7" s="4">
+        <v>29.7</v>
+      </c>
+      <c r="W7" s="5">
+        <v>36612</v>
+      </c>
+      <c r="X7" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y7" s="6">
+        <f t="shared" si="1"/>
+        <v>21.104109589041094</v>
+      </c>
+      <c r="Z7" s="3">
         <f>5*12+9</f>
         <v>69</v>
       </c>
-      <c r="X2" s="3">
+      <c r="AA7" s="3">
+        <v>185</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="3">
+        <v>49</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="1">
+        <v>13</v>
+      </c>
+      <c r="F8" s="3">
+        <v>114</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1258</v>
+      </c>
+      <c r="H8" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>96.769230769230774</v>
+      </c>
+      <c r="I8" s="3">
+        <v>11</v>
+      </c>
+      <c r="J8" s="3">
+        <v>70</v>
+      </c>
+      <c r="K8" s="3">
+        <v>12</v>
+      </c>
+      <c r="L8" s="3">
+        <v>21</v>
+      </c>
+      <c r="M8" s="3">
+        <v>213</v>
+      </c>
+      <c r="N8" s="3">
+        <v>10.1</v>
+      </c>
+      <c r="O8" s="3">
+        <v>2</v>
+      </c>
+      <c r="P8" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="4">
+        <f t="shared" si="0"/>
+        <v>21.853846153846156</v>
+      </c>
+      <c r="R8" s="3">
+        <v>34</v>
+      </c>
+      <c r="S8" s="3">
+        <v>31</v>
+      </c>
+      <c r="T8" s="3">
+        <v>43</v>
+      </c>
+      <c r="U8" s="3">
+        <v>37</v>
+      </c>
+      <c r="V8" s="4">
+        <v>21</v>
+      </c>
+      <c r="W8" s="5">
+        <v>36686</v>
+      </c>
+      <c r="X8" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y8" s="6">
+        <f t="shared" si="1"/>
+        <v>20.901369863013699</v>
+      </c>
+      <c r="Z8" s="3">
+        <f>5*12+9</f>
+        <v>69</v>
+      </c>
+      <c r="AA8" s="3">
         <v>180</v>
       </c>
-      <c r="Y2" s="3">
+      <c r="AB8" s="3">
         <v>18.2</v>
       </c>
-      <c r="Z2" s="3">
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="3">
+        <v>56</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" s="1">
+        <v>6</v>
+      </c>
+      <c r="F9" s="3">
+        <v>33</v>
+      </c>
+      <c r="G9" s="3">
+        <v>768</v>
+      </c>
+      <c r="H9" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>128</v>
+      </c>
+      <c r="I9" s="3">
+        <v>23.3</v>
+      </c>
+      <c r="J9" s="3">
+        <v>85</v>
+      </c>
+      <c r="K9" s="3">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
+        <v>2</v>
+      </c>
+      <c r="M9" s="3">
+        <v>43</v>
+      </c>
+      <c r="N9" s="3">
+        <v>21.5</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="4">
+        <f t="shared" si="0"/>
+        <v>23.933333333333337</v>
+      </c>
+      <c r="R9" s="3">
+        <v>33</v>
+      </c>
+      <c r="S9" s="3">
+        <v>45</v>
+      </c>
+      <c r="T9" s="3">
+        <v>44</v>
+      </c>
+      <c r="U9" s="3">
+        <v>44</v>
+      </c>
+      <c r="V9" s="4">
+        <v>14.2</v>
+      </c>
+      <c r="W9" s="5">
+        <v>35512</v>
+      </c>
+      <c r="X9" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y9" s="6">
+        <f t="shared" si="1"/>
+        <v>24.117808219178084</v>
+      </c>
+      <c r="Z9" s="3">
+        <f>5*12+9</f>
+        <v>69</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>190</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="3">
+        <v>57</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" s="1">
+        <v>13</v>
+      </c>
+      <c r="F10" s="3">
+        <v>69</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1272</v>
+      </c>
+      <c r="H10" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>97.84615384615384</v>
+      </c>
+      <c r="I10" s="3">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="J10" s="3">
+        <v>90</v>
+      </c>
+      <c r="K10" s="3">
+        <v>12</v>
+      </c>
+      <c r="L10" s="3">
         <v>9</v>
       </c>
-      <c r="AA2" s="3">
-        <v>432</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>82.1</v>
-      </c>
-      <c r="AC2" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>9.1222222222222218</v>
-      </c>
-      <c r="AD2" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.1900462962962963</v>
+      <c r="M10" s="3">
+        <v>33</v>
+      </c>
+      <c r="N10" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="4">
+        <f t="shared" si="0"/>
+        <v>17.615384615384617</v>
+      </c>
+      <c r="R10" s="3">
+        <v>39</v>
+      </c>
+      <c r="S10" s="3">
+        <v>42</v>
+      </c>
+      <c r="T10" s="3">
+        <v>38</v>
+      </c>
+      <c r="U10" s="3">
+        <v>39</v>
+      </c>
+      <c r="V10" s="4">
+        <v>22.2</v>
+      </c>
+      <c r="W10" s="5">
+        <v>36440</v>
+      </c>
+      <c r="X10" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y10" s="6">
+        <f t="shared" si="1"/>
+        <v>21.575342465753426</v>
+      </c>
+      <c r="Z10" s="3">
+        <f>5*12+9</f>
+        <v>69</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>165</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C3" s="3">
-        <v>187</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E3" s="1">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3">
-        <v>31</v>
-      </c>
-      <c r="G3" s="3">
-        <v>616</v>
-      </c>
-      <c r="H3" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="I3" s="3">
-        <v>62</v>
-      </c>
-      <c r="J3" s="3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="3">
+        <v>59</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="1">
+        <v>7</v>
+      </c>
+      <c r="F11" s="3">
+        <v>48</v>
+      </c>
+      <c r="G11" s="3">
+        <v>731</v>
+      </c>
+      <c r="H11" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>104.42857142857143</v>
+      </c>
+      <c r="I11" s="3">
+        <v>15.2</v>
+      </c>
+      <c r="J11" s="3">
+        <v>75</v>
+      </c>
+      <c r="K11" s="3">
+        <v>10</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="4">
+        <f t="shared" si="0"/>
+        <v>22.157142857142855</v>
+      </c>
+      <c r="R11" s="3">
+        <v>28</v>
+      </c>
+      <c r="S11" s="3">
+        <v>33</v>
+      </c>
+      <c r="T11" s="3">
+        <v>60</v>
+      </c>
+      <c r="U11" s="3">
+        <v>46</v>
+      </c>
+      <c r="V11" s="4">
+        <v>28.8</v>
+      </c>
+      <c r="W11" s="5">
+        <v>36686</v>
+      </c>
+      <c r="X11" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y11" s="6">
+        <f t="shared" si="1"/>
+        <v>20.901369863013699</v>
+      </c>
+      <c r="Z11" s="3">
+        <f>6*12+3</f>
+        <v>75</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="3">
+        <v>77</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="1">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3">
+        <v>33</v>
+      </c>
+      <c r="G12" s="3">
+        <v>475</v>
+      </c>
+      <c r="H12" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>47.5</v>
+      </c>
+      <c r="I12" s="3">
+        <v>14.4</v>
+      </c>
+      <c r="J12" s="3">
+        <v>36</v>
+      </c>
+      <c r="K12" s="3">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4">
+        <f t="shared" si="0"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="R12" s="3">
+        <v>18</v>
+      </c>
+      <c r="S12" s="3">
+        <v>23</v>
+      </c>
+      <c r="T12" s="3">
+        <v>29</v>
+      </c>
+      <c r="U12" s="3">
+        <v>25</v>
+      </c>
+      <c r="V12" s="4">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5">
+        <v>36425</v>
+      </c>
+      <c r="X12" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y12" s="6">
+        <f t="shared" si="1"/>
+        <v>21.616438356164384</v>
+      </c>
+      <c r="Z12" s="3">
+        <f>6*12+2</f>
+        <v>74</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>210</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="3">
+        <v>82</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="1">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3">
+        <v>55</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1099</v>
+      </c>
+      <c r="H13" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>99.909090909090907</v>
+      </c>
+      <c r="I13" s="3">
+        <v>20</v>
+      </c>
+      <c r="J13" s="3">
+        <v>87</v>
+      </c>
+      <c r="K13" s="3">
         <v>8</v>
       </c>
-      <c r="K3" s="3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="3">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>21</v>
-      </c>
-      <c r="R3" s="3">
-        <v>41</v>
-      </c>
-      <c r="S3" s="3">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4">
+        <f t="shared" si="0"/>
+        <v>16.854545454545455</v>
+      </c>
+      <c r="R13" s="3">
+        <v>25</v>
+      </c>
+      <c r="S13" s="3">
+        <v>33</v>
+      </c>
+      <c r="T13" s="3">
+        <v>28</v>
+      </c>
+      <c r="U13" s="3">
         <v>30</v>
       </c>
-      <c r="T3" s="4">
-        <v>6.3</v>
-      </c>
-      <c r="U3" s="5">
-        <v>35681</v>
-      </c>
-      <c r="V3" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>24.613698630136987</v>
-      </c>
-      <c r="W3" s="3">
+      <c r="V13" s="4">
+        <v>11.4</v>
+      </c>
+      <c r="W13" s="5">
+        <v>36465</v>
+      </c>
+      <c r="X13" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y13" s="6">
+        <f t="shared" si="1"/>
+        <v>21.506849315068493</v>
+      </c>
+      <c r="Z13" s="3">
         <f>6*12+1</f>
         <v>73</v>
       </c>
-      <c r="X3" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z3" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3">
+      <c r="AA13" s="3">
+        <v>185</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AB3" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="AC3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>9.5000000000000001E-2</v>
+      <c r="C14" s="3">
+        <v>85</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" s="1">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3">
+        <v>77</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1020</v>
+      </c>
+      <c r="H14" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>85</v>
+      </c>
+      <c r="I14" s="3">
+        <v>13.2</v>
+      </c>
+      <c r="J14" s="3">
+        <v>83</v>
+      </c>
+      <c r="K14" s="3">
+        <v>7</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="4">
+        <f t="shared" si="0"/>
+        <v>14.875</v>
+      </c>
+      <c r="R14" s="3">
+        <v>24</v>
+      </c>
+      <c r="S14" s="3">
+        <v>24</v>
+      </c>
+      <c r="T14" s="3">
+        <v>23</v>
+      </c>
+      <c r="U14" s="3">
+        <v>23</v>
+      </c>
+      <c r="V14" s="4">
+        <v>18</v>
+      </c>
+      <c r="W14" s="5">
+        <v>36426</v>
+      </c>
+      <c r="X14" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y14" s="6">
+        <f t="shared" si="1"/>
+        <v>21.613698630136987</v>
+      </c>
+      <c r="Z14" s="3">
+        <f>5*12+10</f>
+        <v>70</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>210</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="3">
+        <v>89</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="1">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3">
+        <v>37</v>
+      </c>
+      <c r="G15" s="3">
+        <v>729</v>
+      </c>
+      <c r="H15" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>60.75</v>
+      </c>
+      <c r="I15" s="3">
+        <v>19.7</v>
+      </c>
+      <c r="J15" s="3">
+        <v>76</v>
+      </c>
+      <c r="K15" s="3">
+        <v>7</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <f t="shared" si="0"/>
+        <v>11.116666666666667</v>
+      </c>
+      <c r="R15" s="3">
+        <v>18</v>
+      </c>
+      <c r="S15" s="3">
+        <v>24</v>
+      </c>
+      <c r="T15" s="3">
+        <v>30</v>
+      </c>
+      <c r="U15" s="3">
         <v>27</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E4" s="1">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3">
-        <v>60</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1219</v>
-      </c>
-      <c r="H4" s="3">
-        <v>20.3</v>
-      </c>
-      <c r="I4" s="3">
-        <v>66</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="V15" s="4">
+        <v>29.6</v>
+      </c>
+      <c r="W15" s="5">
+        <v>36238</v>
+      </c>
+      <c r="X15" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y15" s="6">
+        <f t="shared" si="1"/>
+        <v>22.12876712328767</v>
+      </c>
+      <c r="Z15" s="3">
+        <f>6*12+4</f>
+        <v>76</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>215</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="3">
+        <v>91</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E16" s="1">
+        <v>10</v>
+      </c>
+      <c r="F16" s="3">
+        <v>54</v>
+      </c>
+      <c r="G16" s="3">
+        <v>636</v>
+      </c>
+      <c r="H16" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>63.6</v>
+      </c>
+      <c r="I16" s="3">
+        <v>11.8</v>
+      </c>
+      <c r="J16" s="3">
+        <v>91</v>
+      </c>
+      <c r="K16" s="3">
+        <v>3</v>
+      </c>
+      <c r="L16" s="3">
+        <v>4</v>
+      </c>
+      <c r="M16" s="3">
+        <v>-6</v>
+      </c>
+      <c r="N16" s="3">
+        <v>-1.5</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="4">
+        <f t="shared" si="0"/>
+        <v>10.6</v>
+      </c>
+      <c r="R16" s="3">
+        <v>28</v>
+      </c>
+      <c r="S16" s="3">
+        <v>29</v>
+      </c>
+      <c r="T16" s="3">
+        <v>28</v>
+      </c>
+      <c r="U16" s="3">
+        <v>28</v>
+      </c>
+      <c r="V16" s="4">
+        <v>20.2</v>
+      </c>
+      <c r="W16" s="5">
+        <v>36774</v>
+      </c>
+      <c r="X16" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y16" s="6">
+        <f t="shared" si="1"/>
+        <v>20.660273972602738</v>
+      </c>
+      <c r="Z16" s="3">
+        <f>6*12</f>
+        <v>72</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>179</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="3">
+        <v>109</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E17" s="1">
         <v>11</v>
       </c>
-      <c r="K4" s="3">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>37</v>
-      </c>
-      <c r="R4" s="3">
-        <v>35</v>
-      </c>
-      <c r="S4" s="3">
-        <v>36</v>
-      </c>
-      <c r="T4" s="4">
-        <v>21.7</v>
-      </c>
-      <c r="U4" s="5">
-        <v>36462</v>
-      </c>
-      <c r="V4" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.473972602739725</v>
-      </c>
-      <c r="W4" s="3">
+      <c r="F17" s="3">
+        <v>43</v>
+      </c>
+      <c r="G17" s="3">
+        <v>833</v>
+      </c>
+      <c r="H17" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>75.727272727272734</v>
+      </c>
+      <c r="I17" s="3">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="J17" s="3">
+        <v>82</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="4">
+        <f t="shared" si="0"/>
+        <v>10.981818181818182</v>
+      </c>
+      <c r="R17" s="3">
+        <v>21</v>
+      </c>
+      <c r="S17" s="3">
+        <v>31</v>
+      </c>
+      <c r="T17" s="3">
+        <v>15</v>
+      </c>
+      <c r="U17" s="3">
+        <v>23</v>
+      </c>
+      <c r="V17" s="4">
+        <v>52.6</v>
+      </c>
+      <c r="W17" s="5">
+        <v>35781</v>
+      </c>
+      <c r="X17" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y17" s="6">
+        <f t="shared" si="1"/>
+        <v>23.38082191780822</v>
+      </c>
+      <c r="Z17" s="3">
         <f>6*12+2</f>
         <v>74</v>
       </c>
-      <c r="X4" s="3">
+      <c r="AA17" s="3">
         <v>210</v>
       </c>
-      <c r="Y4" s="3">
-        <v>18.8</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>12</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>604</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>80.5</v>
-      </c>
-      <c r="AC4" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>6.708333333333333</v>
-      </c>
-      <c r="AD4" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.13327814569536423</v>
+      <c r="AB17" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="3">
+        <v>112</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" s="1">
+        <v>6</v>
+      </c>
+      <c r="F18" s="3">
+        <v>41</v>
+      </c>
+      <c r="G18" s="3">
+        <v>478</v>
+      </c>
+      <c r="H18" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>79.666666666666671</v>
+      </c>
+      <c r="I18" s="3">
+        <v>11.7</v>
+      </c>
+      <c r="J18" s="3">
+        <v>48</v>
+      </c>
+      <c r="K18" s="3">
+        <v>7</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4">
+        <f t="shared" si="0"/>
+        <v>18.383333333333333</v>
+      </c>
+      <c r="R18" s="3">
+        <v>23</v>
+      </c>
+      <c r="S18" s="3">
+        <v>25</v>
+      </c>
+      <c r="T18" s="3">
+        <v>41</v>
+      </c>
+      <c r="U18" s="3">
+        <v>33</v>
+      </c>
+      <c r="V18" s="4">
+        <v>80.2</v>
+      </c>
+      <c r="W18" s="5">
+        <v>36457</v>
+      </c>
+      <c r="X18" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y18" s="6">
+        <f t="shared" si="1"/>
+        <v>21.528767123287672</v>
+      </c>
+      <c r="Z18" s="3">
+        <f>6*12+1</f>
+        <v>73</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>195</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="3">
+        <v>129</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" s="1">
+        <v>9</v>
+      </c>
+      <c r="F19" s="3">
+        <v>74</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1190</v>
+      </c>
+      <c r="H19" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>132.22222222222223</v>
+      </c>
+      <c r="I19" s="3">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="J19" s="3">
+        <v>75</v>
+      </c>
+      <c r="K19" s="3">
+        <v>19</v>
+      </c>
+      <c r="L19" s="3">
+        <v>2</v>
+      </c>
+      <c r="M19" s="3">
+        <v>-1</v>
+      </c>
+      <c r="N19" s="3">
+        <v>-0.5</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4">
+        <f t="shared" si="0"/>
+        <v>29.988888888888887</v>
+      </c>
+      <c r="R19" s="3">
+        <v>44</v>
+      </c>
+      <c r="S19" s="3">
+        <v>47</v>
+      </c>
+      <c r="T19" s="3">
+        <v>75</v>
+      </c>
+      <c r="U19" s="3">
+        <v>61</v>
+      </c>
+      <c r="V19" s="4">
+        <v>0</v>
+      </c>
+      <c r="W19" s="5">
+        <v>36174</v>
+      </c>
+      <c r="X19" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y19" s="6">
+        <f t="shared" si="1"/>
+        <v>22.304109589041097</v>
+      </c>
+      <c r="Z19" s="3">
+        <f>5*12+9</f>
+        <v>69</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>174</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C20" s="3">
         <v>131</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D20" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E20" s="1">
         <v>10</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F20" s="3">
         <v>59</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G20" s="3">
         <v>917</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H20" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>91.7</v>
+      </c>
+      <c r="I20" s="3">
         <v>15.5</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J20" s="3">
         <v>55</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K20" s="3">
         <v>6</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L20" s="3">
         <v>1</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M20" s="3">
         <v>7</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N20" s="3">
         <v>7</v>
       </c>
-      <c r="N5" s="3">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4">
+        <f t="shared" si="0"/>
+        <v>15.789999999999997</v>
+      </c>
+      <c r="R20" s="3">
         <v>31</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="S20" s="3">
         <v>38</v>
       </c>
-      <c r="R5" s="3">
+      <c r="T20" s="3">
         <v>37</v>
       </c>
-      <c r="S5" s="3">
+      <c r="U20" s="3">
         <v>37</v>
       </c>
-      <c r="T5" s="4">
+      <c r="V20" s="4">
         <v>21.7</v>
       </c>
-      <c r="U5" s="5">
+      <c r="W20" s="5">
         <v>36293</v>
       </c>
-      <c r="V5" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.936986301369863</v>
-      </c>
-      <c r="W5" s="3">
+      <c r="X20" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y20" s="6">
+        <f t="shared" si="1"/>
+        <v>21.978082191780821</v>
+      </c>
+      <c r="Z20" s="3">
         <f>6*12</f>
         <v>72</v>
       </c>
-      <c r="X5" s="3">
+      <c r="AA20" s="3">
         <v>190</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="AB20" s="3">
         <v>19.3</v>
       </c>
-      <c r="Z5" s="3">
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="3">
+        <v>157</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" s="1">
+        <v>7</v>
+      </c>
+      <c r="F21" s="3">
+        <v>25</v>
+      </c>
+      <c r="G21" s="3">
+        <v>345</v>
+      </c>
+      <c r="H21" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>49.285714285714285</v>
+      </c>
+      <c r="I21" s="3">
+        <v>13.8</v>
+      </c>
+      <c r="J21" s="3">
+        <v>53</v>
+      </c>
+      <c r="K21" s="3">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3">
+        <v>7</v>
+      </c>
+      <c r="M21" s="3">
+        <v>54</v>
+      </c>
+      <c r="N21" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="O21" s="3">
         <v>1</v>
       </c>
-      <c r="AA5" s="3">
-        <v>84</v>
-      </c>
-      <c r="AB5" s="3">
-        <v>3.3</v>
-      </c>
-      <c r="AC5" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>3.3</v>
-      </c>
-      <c r="AD5" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>3.9285714285714285E-2</v>
+      <c r="P21" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="4">
+        <f t="shared" si="0"/>
+        <v>11.485714285714286</v>
+      </c>
+      <c r="R21" s="3">
+        <v>20</v>
+      </c>
+      <c r="S21" s="3">
+        <v>25</v>
+      </c>
+      <c r="T21" s="3">
+        <v>51</v>
+      </c>
+      <c r="U21" s="3">
+        <v>37</v>
+      </c>
+      <c r="V21" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="W21" s="5">
+        <v>36401</v>
+      </c>
+      <c r="X21" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y21" s="6">
+        <f t="shared" si="1"/>
+        <v>21.682191780821917</v>
+      </c>
+      <c r="Z21" s="3">
+        <f>6*12+1</f>
+        <v>73</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>179</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="3">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="3">
+        <v>179</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E22" s="1">
+        <v>6</v>
+      </c>
+      <c r="F22" s="3">
+        <v>37</v>
+      </c>
+      <c r="G22" s="3">
+        <v>584</v>
+      </c>
+      <c r="H22" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>97.333333333333329</v>
+      </c>
+      <c r="I22" s="3">
+        <v>15.8</v>
+      </c>
+      <c r="J22" s="3">
+        <v>57</v>
+      </c>
+      <c r="K22" s="3">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1</v>
+      </c>
+      <c r="M22" s="3">
+        <v>-1</v>
+      </c>
+      <c r="N22" s="3">
+        <v>-1</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4">
+        <f t="shared" si="0"/>
+        <v>15.800000000000002</v>
+      </c>
+      <c r="R22" s="3">
+        <v>26</v>
+      </c>
+      <c r="S22" s="3">
+        <v>34</v>
+      </c>
+      <c r="T22" s="3">
+        <v>43</v>
+      </c>
+      <c r="U22" s="3">
+        <v>38</v>
+      </c>
+      <c r="V22" s="4">
+        <v>0</v>
+      </c>
+      <c r="W22" s="5">
+        <v>35739</v>
+      </c>
+      <c r="X22" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y22" s="6">
+        <f t="shared" si="1"/>
+        <v>23.495890410958904</v>
+      </c>
+      <c r="Z22" s="3">
+        <f>6*12+4</f>
+        <v>76</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>227</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="3">
+        <v>187</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="1">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3">
+        <v>31</v>
+      </c>
+      <c r="G23" s="3">
+        <v>616</v>
+      </c>
+      <c r="H23" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>51.333333333333336</v>
+      </c>
+      <c r="I23" s="3">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="J23" s="3">
+        <v>62</v>
+      </c>
+      <c r="K23" s="3">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4">
+        <f t="shared" si="0"/>
+        <v>10.424999999999999</v>
+      </c>
+      <c r="R23" s="3">
+        <v>14</v>
+      </c>
+      <c r="S23" s="3">
+        <v>21</v>
+      </c>
+      <c r="T23" s="3">
+        <v>41</v>
+      </c>
+      <c r="U23" s="3">
+        <v>30</v>
+      </c>
+      <c r="V23" s="4">
+        <v>6.3</v>
+      </c>
+      <c r="W23" s="5">
+        <v>35681</v>
+      </c>
+      <c r="X23" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y23" s="6">
+        <f t="shared" si="1"/>
+        <v>23.654794520547945</v>
+      </c>
+      <c r="Z23" s="3">
+        <f>6*12+1</f>
+        <v>73</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3">
         <v>203</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D24" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" s="1">
         <v>13</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F24" s="3">
         <v>75</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G24" s="3">
         <v>1019</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H24" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>78.384615384615387</v>
+      </c>
+      <c r="I24" s="3">
         <v>13.6</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J24" s="3">
         <v>79</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K24" s="3">
         <v>9</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L24" s="3">
         <v>14</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M24" s="3">
         <v>126</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N24" s="3">
         <v>9</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O24" s="3">
         <v>2</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P24" s="3">
         <v>3</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q24" s="4">
+        <f t="shared" si="0"/>
+        <v>16.307692307692307</v>
+      </c>
+      <c r="R24" s="3">
         <v>26</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="S24" s="3">
         <v>26</v>
       </c>
-      <c r="R6" s="3">
+      <c r="T24" s="3">
         <v>20</v>
       </c>
-      <c r="S6" s="3">
+      <c r="U24" s="3">
         <v>23</v>
       </c>
-      <c r="T6" s="4">
+      <c r="V24" s="4">
         <v>12.2</v>
       </c>
-      <c r="U6" s="5">
+      <c r="W24" s="5">
         <v>35880</v>
       </c>
-      <c r="V6" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>24.068493150684933</v>
-      </c>
-      <c r="W6" s="3">
+      <c r="X24" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y24" s="6">
+        <f t="shared" si="1"/>
+        <v>23.109589041095891</v>
+      </c>
+      <c r="Z24" s="3">
         <f>6*12</f>
         <v>72</v>
       </c>
-      <c r="X6" s="3">
+      <c r="AA24" s="3">
         <v>190</v>
       </c>
-      <c r="Y6" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="3">
+        <v>204</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E25" s="1">
+        <v>9</v>
+      </c>
+      <c r="F25" s="3">
+        <v>57</v>
+      </c>
+      <c r="G25" s="3">
+        <v>633</v>
+      </c>
+      <c r="H25" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>70.333333333333329</v>
+      </c>
+      <c r="I25" s="3">
+        <v>11.1</v>
+      </c>
+      <c r="J25" s="3">
+        <v>36</v>
+      </c>
+      <c r="K25" s="3">
+        <v>4</v>
+      </c>
+      <c r="L25" s="3">
         <v>6</v>
       </c>
-      <c r="AB6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0</v>
+      <c r="M25" s="3">
+        <v>6</v>
+      </c>
+      <c r="N25" s="3">
+        <v>1</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="4">
+        <f t="shared" si="0"/>
+        <v>12.71111111111111</v>
+      </c>
+      <c r="R25" s="3">
+        <v>36</v>
+      </c>
+      <c r="S25" s="3">
+        <v>38</v>
+      </c>
+      <c r="T25" s="3">
+        <v>56</v>
+      </c>
+      <c r="U25" s="3">
+        <v>46</v>
+      </c>
+      <c r="V25" s="4">
+        <v>28.8</v>
+      </c>
+      <c r="W25" s="5">
+        <v>36094</v>
+      </c>
+      <c r="X25" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y25" s="6">
+        <f t="shared" si="1"/>
+        <v>22.523287671232875</v>
+      </c>
+      <c r="Z25" s="3">
+        <f>5*12+10</f>
+        <v>70</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>190</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="3">
-        <v>59</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="1">
-        <v>7</v>
-      </c>
-      <c r="F7" s="3">
-        <v>48</v>
-      </c>
-      <c r="G7" s="3">
-        <v>731</v>
-      </c>
-      <c r="H7" s="3">
-        <v>15.2</v>
-      </c>
-      <c r="I7" s="3">
-        <v>75</v>
-      </c>
-      <c r="J7" s="3">
-        <v>10</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="3">
+        <v>219</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E26" s="1">
+        <v>11</v>
+      </c>
+      <c r="F26" s="3">
+        <v>47</v>
+      </c>
+      <c r="G26" s="3">
+        <v>760</v>
+      </c>
+      <c r="H26" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>69.090909090909093</v>
+      </c>
+      <c r="I26" s="3">
+        <v>16.2</v>
+      </c>
+      <c r="J26" s="3">
+        <v>58</v>
+      </c>
+      <c r="K26" s="3">
+        <v>4</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>1</v>
       </c>
-      <c r="P7" s="3">
-        <v>28</v>
-      </c>
-      <c r="Q7" s="3">
+      <c r="Q26" s="4">
+        <f t="shared" si="0"/>
+        <v>11.045454545454545</v>
+      </c>
+      <c r="R26" s="3">
+        <v>22</v>
+      </c>
+      <c r="S26" s="3">
+        <v>31</v>
+      </c>
+      <c r="T26" s="3">
         <v>33</v>
       </c>
-      <c r="R7" s="3">
-        <v>60</v>
-      </c>
-      <c r="S7" s="3">
-        <v>46</v>
-      </c>
-      <c r="T7" s="4">
-        <v>28.8</v>
-      </c>
-      <c r="U7" s="5">
-        <v>36686</v>
-      </c>
-      <c r="V7" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>21.860273972602741</v>
-      </c>
-      <c r="W7" s="3">
+      <c r="U26" s="3">
+        <v>32</v>
+      </c>
+      <c r="V26" s="4">
+        <v>0</v>
+      </c>
+      <c r="W26" s="5">
+        <v>36626</v>
+      </c>
+      <c r="X26" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y26" s="6">
+        <f t="shared" si="1"/>
+        <v>21.065753424657533</v>
+      </c>
+      <c r="Z26" s="3">
         <f>6*12+3</f>
         <v>75</v>
       </c>
-      <c r="X7" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>19.2</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>8</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>422</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>24.3</v>
-      </c>
-      <c r="AC7" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>3.0375000000000001</v>
-      </c>
-      <c r="AD7" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>5.7582938388625597E-2</v>
+      <c r="AA26" s="3">
+        <v>211</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="3">
-        <v>204</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="1">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="3">
+        <v>221</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E27" s="1">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3">
+        <v>72</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1018</v>
+      </c>
+      <c r="H27" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>84.833333333333329</v>
+      </c>
+      <c r="I27" s="3">
+        <v>14.1</v>
+      </c>
+      <c r="J27" s="3">
+        <v>57</v>
+      </c>
+      <c r="K27" s="3">
+        <v>10</v>
+      </c>
+      <c r="L27" s="3">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3">
         <v>9</v>
       </c>
-      <c r="F8" s="3">
-        <v>57</v>
-      </c>
-      <c r="G8" s="3">
-        <v>633</v>
-      </c>
-      <c r="H8" s="3">
-        <v>11.1</v>
-      </c>
-      <c r="I8" s="3">
-        <v>36</v>
-      </c>
-      <c r="J8" s="3">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
-        <v>6</v>
-      </c>
-      <c r="L8" s="3">
-        <v>6</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="N27" s="3">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>1</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>1</v>
-      </c>
-      <c r="P8" s="3">
-        <v>36</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>38</v>
-      </c>
-      <c r="R8" s="3">
-        <v>56</v>
-      </c>
-      <c r="S8" s="3">
-        <v>46</v>
-      </c>
-      <c r="T8" s="4">
-        <v>28.8</v>
-      </c>
-      <c r="U8" s="5">
-        <v>36094</v>
-      </c>
-      <c r="V8" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>23.482191780821918</v>
-      </c>
-      <c r="W8" s="3">
-        <f>5*12+10</f>
-        <v>70</v>
-      </c>
-      <c r="X8" s="3">
-        <v>190</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>85</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>13.1</v>
-      </c>
-      <c r="AC8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.15411764705882353</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="3">
-        <v>221</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="1">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3">
-        <v>72</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1018</v>
-      </c>
-      <c r="H9" s="3">
-        <v>14.1</v>
-      </c>
-      <c r="I9" s="3">
-        <v>57</v>
-      </c>
-      <c r="J9" s="3">
-        <v>10</v>
-      </c>
-      <c r="K9" s="3">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3">
-        <v>9</v>
-      </c>
-      <c r="M9" s="3">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3">
-        <v>1</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q27" s="4">
+        <f t="shared" si="0"/>
+        <v>16.391666666666669</v>
+      </c>
+      <c r="R27" s="3">
         <v>29</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S27" s="3">
         <v>30</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T27" s="3">
         <v>28</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U27" s="3">
         <v>28</v>
       </c>
-      <c r="T9" s="4">
+      <c r="V27" s="4">
         <v>67</v>
       </c>
-      <c r="U9" s="5">
+      <c r="W27" s="5">
         <v>36295</v>
       </c>
-      <c r="V9" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.931506849315067</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="X27" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y27" s="6">
+        <f t="shared" si="1"/>
+        <v>21.972602739726028</v>
+      </c>
+      <c r="Z27" s="3">
         <f>5*12+11</f>
         <v>71</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AA27" s="3">
         <v>190</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AB27" s="3">
         <v>20.3</v>
       </c>
-      <c r="Z9" s="3">
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3">
+        <v>258</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" s="1">
+        <v>12</v>
+      </c>
+      <c r="F28" s="3">
+        <v>70</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1188</v>
+      </c>
+      <c r="H28" s="6">
+        <f>Table7[[#This Row],[Rec.Yds]]/Table7[[#This Row],[College Games]]</f>
+        <v>99</v>
+      </c>
+      <c r="I28" s="3">
+        <v>17</v>
+      </c>
+      <c r="J28" s="3">
+        <v>78</v>
+      </c>
+      <c r="K28" s="3">
+        <v>8</v>
+      </c>
+      <c r="L28" s="3">
+        <v>11</v>
+      </c>
+      <c r="M28" s="3">
+        <v>67</v>
+      </c>
+      <c r="N28" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
         <v>2</v>
       </c>
-      <c r="AA9" s="3">
-        <v>103</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>3.3</v>
-      </c>
-      <c r="AC9" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>1.65</v>
-      </c>
-      <c r="AD9" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>3.2038834951456312E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="3">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="1">
-        <v>14</v>
-      </c>
-      <c r="F10" s="3">
-        <v>84</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1780</v>
-      </c>
-      <c r="H10" s="3">
-        <v>21.2</v>
-      </c>
-      <c r="I10" s="3">
-        <v>78</v>
-      </c>
-      <c r="J10" s="3">
-        <v>20</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1</v>
-      </c>
-      <c r="L10" s="3">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1</v>
-      </c>
-      <c r="P10" s="3">
-        <v>21</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>32</v>
-      </c>
-      <c r="R10" s="3">
-        <v>35</v>
-      </c>
-      <c r="S10" s="3">
-        <v>33</v>
-      </c>
-      <c r="T10" s="4">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="U10" s="5">
-        <v>36586</v>
-      </c>
-      <c r="V10" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.134246575342466</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="Q28" s="4">
+        <f t="shared" si="0"/>
+        <v>17.041666666666668</v>
+      </c>
+      <c r="R28" s="3">
+        <v>26</v>
+      </c>
+      <c r="S28" s="3">
+        <v>30</v>
+      </c>
+      <c r="T28" s="3">
+        <v>24</v>
+      </c>
+      <c r="U28" s="3">
+        <v>26</v>
+      </c>
+      <c r="V28" s="4">
+        <v>11.4</v>
+      </c>
+      <c r="W28" s="5">
+        <v>36334</v>
+      </c>
+      <c r="X28" s="5">
+        <v>44315</v>
+      </c>
+      <c r="Y28" s="6">
+        <f t="shared" si="1"/>
+        <v>21.865753424657534</v>
+      </c>
+      <c r="Z28" s="3">
         <f>6*12</f>
         <v>72</v>
       </c>
-      <c r="X10" s="3">
-        <v>208</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>19.5</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>16</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>940</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>263.10000000000002</v>
-      </c>
-      <c r="AC10" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>16.443750000000001</v>
-      </c>
-      <c r="AD10" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.27989361702127663</v>
+      <c r="AA28" s="3">
+        <v>190</v>
+      </c>
+      <c r="AB28" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="3">
-        <v>91</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E11" s="1">
-        <v>10</v>
-      </c>
-      <c r="F11" s="3">
-        <v>54</v>
-      </c>
-      <c r="G11" s="3">
-        <v>636</v>
-      </c>
-      <c r="H11" s="3">
-        <v>11.8</v>
-      </c>
-      <c r="I11" s="3">
-        <v>91</v>
-      </c>
-      <c r="J11" s="3">
-        <v>3</v>
-      </c>
-      <c r="K11" s="3">
-        <v>4</v>
-      </c>
-      <c r="L11" s="3">
-        <v>-6</v>
-      </c>
-      <c r="M11" s="3">
-        <v>-1.5</v>
-      </c>
-      <c r="N11" s="3">
-        <v>0</v>
-      </c>
-      <c r="O11" s="3">
-        <v>1</v>
-      </c>
-      <c r="P11" s="3">
-        <v>28</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>29</v>
-      </c>
-      <c r="R11" s="3">
-        <v>28</v>
-      </c>
-      <c r="S11" s="3">
-        <v>28</v>
-      </c>
-      <c r="T11" s="4">
-        <v>20.2</v>
-      </c>
-      <c r="U11" s="5">
-        <v>36774</v>
-      </c>
-      <c r="V11" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>21.61917808219178</v>
-      </c>
-      <c r="W11" s="3">
-        <f>6*12</f>
-        <v>72</v>
-      </c>
-      <c r="X11" s="3">
-        <v>179</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>20</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>6</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>295</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>28.4</v>
-      </c>
-      <c r="AC11" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>4.7333333333333334</v>
-      </c>
-      <c r="AD11" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>9.6271186440677961E-2</v>
-      </c>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="V29" s="4"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="3">
-        <v>179</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E12" s="1">
-        <v>6</v>
-      </c>
-      <c r="F12" s="3">
-        <v>37</v>
-      </c>
-      <c r="G12" s="3">
-        <v>584</v>
-      </c>
-      <c r="H12" s="3">
-        <v>15.8</v>
-      </c>
-      <c r="I12" s="3">
-        <v>57</v>
-      </c>
-      <c r="J12" s="3">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1</v>
-      </c>
-      <c r="L12" s="3">
-        <v>-1</v>
-      </c>
-      <c r="M12" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3">
-        <v>26</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>34</v>
-      </c>
-      <c r="R12" s="3">
-        <v>43</v>
-      </c>
-      <c r="S12" s="3">
-        <v>38</v>
-      </c>
-      <c r="T12" s="4">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5">
-        <v>35739</v>
-      </c>
-      <c r="V12" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>24.454794520547946</v>
-      </c>
-      <c r="W12" s="3">
-        <f>6*12+4</f>
-        <v>76</v>
-      </c>
-      <c r="X12" s="3">
-        <v>227</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>21.8</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>7</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="3">
-        <v>219</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" s="1">
-        <v>11</v>
-      </c>
-      <c r="F13" s="3">
-        <v>47</v>
-      </c>
-      <c r="G13" s="3">
-        <v>760</v>
-      </c>
-      <c r="H13" s="3">
-        <v>16.2</v>
-      </c>
-      <c r="I13" s="3">
-        <v>58</v>
-      </c>
-      <c r="J13" s="3">
-        <v>4</v>
-      </c>
-      <c r="K13" s="3">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3">
-        <v>0</v>
-      </c>
-      <c r="O13" s="3">
-        <v>1</v>
-      </c>
-      <c r="P13" s="3">
-        <v>22</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>31</v>
-      </c>
-      <c r="R13" s="3">
-        <v>33</v>
-      </c>
-      <c r="S13" s="3">
-        <v>32</v>
-      </c>
-      <c r="T13" s="4">
-        <v>0</v>
-      </c>
-      <c r="U13" s="5">
-        <v>36626</v>
-      </c>
-      <c r="V13" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.024657534246575</v>
-      </c>
-      <c r="W13" s="3">
-        <f>6*12+3</f>
-        <v>75</v>
-      </c>
-      <c r="X13" s="3">
-        <v>211</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="3">
-        <v>49</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>3.9</v>
-      </c>
-      <c r="AC13" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>3.9</v>
-      </c>
-      <c r="AD13" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>7.9591836734693874E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="3">
-        <v>112</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E14" s="1">
-        <v>6</v>
-      </c>
-      <c r="F14" s="3">
-        <v>41</v>
-      </c>
-      <c r="G14" s="3">
-        <v>478</v>
-      </c>
-      <c r="H14" s="3">
-        <v>11.7</v>
-      </c>
-      <c r="I14" s="3">
-        <v>48</v>
-      </c>
-      <c r="J14" s="3">
-        <v>7</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>23</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>25</v>
-      </c>
-      <c r="R14" s="3">
-        <v>41</v>
-      </c>
-      <c r="S14" s="3">
-        <v>33</v>
-      </c>
-      <c r="T14" s="4">
-        <v>80.2</v>
-      </c>
-      <c r="U14" s="5">
-        <v>36457</v>
-      </c>
-      <c r="V14" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.487671232876714</v>
-      </c>
-      <c r="W14" s="3">
-        <f>6*12+1</f>
-        <v>73</v>
-      </c>
-      <c r="X14" s="3">
-        <v>195</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>17</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>816</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>182.3</v>
-      </c>
-      <c r="AC14" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>10.723529411764707</v>
-      </c>
-      <c r="AD14" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.22340686274509805</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="3">
-        <v>85</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E15" s="1">
-        <v>12</v>
-      </c>
-      <c r="F15" s="3">
-        <v>77</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1020</v>
-      </c>
-      <c r="H15" s="3">
-        <v>13.2</v>
-      </c>
-      <c r="I15" s="3">
-        <v>83</v>
-      </c>
-      <c r="J15" s="3">
-        <v>7</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>2</v>
-      </c>
-      <c r="P15" s="3">
-        <v>24</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>24</v>
-      </c>
-      <c r="R15" s="3">
-        <v>23</v>
-      </c>
-      <c r="S15" s="3">
-        <v>23</v>
-      </c>
-      <c r="T15" s="4">
-        <v>18</v>
-      </c>
-      <c r="U15" s="5">
-        <v>36426</v>
-      </c>
-      <c r="V15" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.572602739726026</v>
-      </c>
-      <c r="W15" s="3">
-        <f>5*12+10</f>
-        <v>70</v>
-      </c>
-      <c r="X15" s="3">
-        <v>210</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>21</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>103</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="AC15" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>7.6</v>
-      </c>
-      <c r="AD15" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>7.3786407766990289E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="3">
-        <v>89</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E16" s="1">
-        <v>12</v>
-      </c>
-      <c r="F16" s="3">
-        <v>37</v>
-      </c>
-      <c r="G16" s="3">
-        <v>729</v>
-      </c>
-      <c r="H16" s="3">
-        <v>19.7</v>
-      </c>
-      <c r="I16" s="3">
-        <v>76</v>
-      </c>
-      <c r="J16" s="3">
-        <v>7</v>
-      </c>
-      <c r="K16" s="3">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3">
-        <v>0</v>
-      </c>
-      <c r="O16" s="3">
-        <v>0</v>
-      </c>
-      <c r="P16" s="3">
-        <v>18</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>24</v>
-      </c>
-      <c r="R16" s="3">
-        <v>30</v>
-      </c>
-      <c r="S16" s="3">
-        <v>27</v>
-      </c>
-      <c r="T16" s="4">
-        <v>29.6</v>
-      </c>
-      <c r="U16" s="5">
-        <v>36238</v>
-      </c>
-      <c r="V16" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>23.087671232876712</v>
-      </c>
-      <c r="W16" s="3">
-        <f>6*12+4</f>
-        <v>76</v>
-      </c>
-      <c r="X16" s="3">
-        <v>215</v>
-      </c>
-      <c r="Y16" s="3">
-        <v>19.5</v>
-      </c>
-      <c r="Z16" s="3">
-        <v>13</v>
-      </c>
-      <c r="AA16" s="3">
-        <v>536</v>
-      </c>
-      <c r="AB16" s="3">
-        <v>67.099999999999994</v>
-      </c>
-      <c r="AC16" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>5.161538461538461</v>
-      </c>
-      <c r="AD16" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.12518656716417909</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="3">
-        <v>77</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E17" s="1">
-        <v>10</v>
-      </c>
-      <c r="F17" s="3">
-        <v>33</v>
-      </c>
-      <c r="G17" s="3">
-        <v>475</v>
-      </c>
-      <c r="H17" s="3">
-        <v>14.4</v>
-      </c>
-      <c r="I17" s="3">
-        <v>36</v>
-      </c>
-      <c r="J17" s="3">
-        <v>4</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3">
-        <v>18</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>23</v>
-      </c>
-      <c r="R17" s="3">
-        <v>29</v>
-      </c>
-      <c r="S17" s="3">
-        <v>25</v>
-      </c>
-      <c r="T17" s="4">
-        <v>0</v>
-      </c>
-      <c r="U17" s="5">
-        <v>36425</v>
-      </c>
-      <c r="V17" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.575342465753426</v>
-      </c>
-      <c r="W17" s="3">
-        <f>6*12+2</f>
-        <v>74</v>
-      </c>
-      <c r="X17" s="3">
-        <v>210</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>7</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>459</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="AC17" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>10.914285714285715</v>
-      </c>
-      <c r="AD17" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.1664488017429194</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="3">
-        <v>57</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E18" s="1">
-        <v>13</v>
-      </c>
-      <c r="F18" s="3">
-        <v>69</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1272</v>
-      </c>
-      <c r="H18" s="3">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="I18" s="3">
-        <v>90</v>
-      </c>
-      <c r="J18" s="3">
-        <v>12</v>
-      </c>
-      <c r="K18" s="3">
-        <v>9</v>
-      </c>
-      <c r="L18" s="3">
-        <v>33</v>
-      </c>
-      <c r="M18" s="3">
-        <v>3.7</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3">
-        <v>39</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>42</v>
-      </c>
-      <c r="R18" s="3">
-        <v>38</v>
-      </c>
-      <c r="S18" s="3">
-        <v>39</v>
-      </c>
-      <c r="T18" s="4">
-        <v>22.2</v>
-      </c>
-      <c r="U18" s="5">
-        <v>36440</v>
-      </c>
-      <c r="V18" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.534246575342465</v>
-      </c>
-      <c r="W18" s="3">
-        <f>5*12+9</f>
-        <v>69</v>
-      </c>
-      <c r="X18" s="3">
-        <v>165</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>10</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="3">
-        <v>6</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" s="1">
-        <v>6</v>
-      </c>
-      <c r="F19" s="3">
-        <v>28</v>
-      </c>
-      <c r="G19" s="3">
-        <v>591</v>
-      </c>
-      <c r="H19" s="3">
-        <v>21.1</v>
-      </c>
-      <c r="I19" s="3">
-        <v>90</v>
-      </c>
-      <c r="J19" s="3">
-        <v>4</v>
-      </c>
-      <c r="K19" s="3">
-        <v>3</v>
-      </c>
-      <c r="L19" s="3">
-        <v>12</v>
-      </c>
-      <c r="M19" s="3">
-        <v>4</v>
-      </c>
-      <c r="N19" s="3">
-        <v>0</v>
-      </c>
-      <c r="O19" s="3">
-        <v>0</v>
-      </c>
-      <c r="P19" s="3">
-        <v>19</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>28</v>
-      </c>
-      <c r="R19" s="3">
-        <v>21</v>
-      </c>
-      <c r="S19" s="3">
-        <v>24</v>
-      </c>
-      <c r="T19" s="4">
-        <v>14</v>
-      </c>
-      <c r="U19" s="5">
-        <v>36093</v>
-      </c>
-      <c r="V19" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>23.484931506849314</v>
-      </c>
-      <c r="W19" s="3">
-        <f>5*12+10</f>
-        <v>70</v>
-      </c>
-      <c r="X19" s="3">
-        <v>182</v>
-      </c>
-      <c r="Y19" s="3">
-        <v>21.8</v>
-      </c>
-      <c r="Z19" s="3">
-        <v>16</v>
-      </c>
-      <c r="AA19" s="3">
-        <v>903</v>
-      </c>
-      <c r="AB19" s="3">
-        <v>193.8</v>
-      </c>
-      <c r="AC19" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>12.112500000000001</v>
-      </c>
-      <c r="AD19" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.21461794019933556</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="3">
-        <v>157</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E20" s="1">
-        <v>7</v>
-      </c>
-      <c r="F20" s="3">
-        <v>25</v>
-      </c>
-      <c r="G20" s="3">
-        <v>345</v>
-      </c>
-      <c r="H20" s="3">
-        <v>13.8</v>
-      </c>
-      <c r="I20" s="3">
-        <v>53</v>
-      </c>
-      <c r="J20" s="3">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
-        <v>7</v>
-      </c>
-      <c r="L20" s="3">
-        <v>54</v>
-      </c>
-      <c r="M20" s="3">
-        <v>7.7</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1</v>
-      </c>
-      <c r="O20" s="3">
-        <v>1</v>
-      </c>
-      <c r="P20" s="3">
-        <v>20</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>25</v>
-      </c>
-      <c r="R20" s="3">
-        <v>51</v>
-      </c>
-      <c r="S20" s="3">
-        <v>37</v>
-      </c>
-      <c r="T20" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="U20" s="5">
-        <v>36401</v>
-      </c>
-      <c r="V20" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.641095890410959</v>
-      </c>
-      <c r="W20" s="3">
-        <f>6*12+1</f>
-        <v>73</v>
-      </c>
-      <c r="X20" s="3">
-        <v>179</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>20</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>2</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>86</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>26.1</v>
-      </c>
-      <c r="AC20" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>13.05</v>
-      </c>
-      <c r="AD20" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.30348837209302326</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="3">
-        <v>20</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E21" s="1">
-        <v>11</v>
-      </c>
-      <c r="F21" s="3">
-        <v>70</v>
-      </c>
-      <c r="G21" s="3">
-        <v>984</v>
-      </c>
-      <c r="H21" s="3">
-        <v>14.1</v>
-      </c>
-      <c r="I21" s="3">
-        <v>57</v>
-      </c>
-      <c r="J21" s="3">
-        <v>10</v>
-      </c>
-      <c r="K21" s="3">
-        <v>19</v>
-      </c>
-      <c r="L21" s="3">
-        <v>161</v>
-      </c>
-      <c r="M21" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="N21" s="3">
-        <v>1</v>
-      </c>
-      <c r="O21" s="3">
-        <v>1</v>
-      </c>
-      <c r="P21" s="3">
-        <v>24</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>24</v>
-      </c>
-      <c r="R21" s="3">
-        <v>24</v>
-      </c>
-      <c r="S21" s="3">
-        <v>23</v>
-      </c>
-      <c r="T21" s="4">
-        <v>24.2</v>
-      </c>
-      <c r="U21" s="5">
-        <v>36187</v>
-      </c>
-      <c r="V21" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>23.227397260273971</v>
-      </c>
-      <c r="W21" s="3">
-        <f>6*12</f>
-        <v>72</v>
-      </c>
-      <c r="X21" s="3">
-        <v>193</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>21.6</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>7</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>301</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>62.86</v>
-      </c>
-      <c r="AC21" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>8.98</v>
-      </c>
-      <c r="AD21" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.20883720930232558</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C22" s="3">
-        <v>34</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E22" s="1">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3">
-        <v>86</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1193</v>
-      </c>
-      <c r="H22" s="3">
-        <v>13.9</v>
-      </c>
-      <c r="I22" s="3">
-        <v>91</v>
-      </c>
-      <c r="J22" s="3">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
-        <v>14</v>
-      </c>
-      <c r="L22" s="3">
-        <v>64</v>
-      </c>
-      <c r="M22" s="3">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1</v>
-      </c>
-      <c r="P22" s="3">
-        <v>45</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>43</v>
-      </c>
-      <c r="R22" s="3">
-        <v>33</v>
-      </c>
-      <c r="S22" s="3">
-        <v>38</v>
-      </c>
-      <c r="T22" s="4">
-        <v>29.7</v>
-      </c>
-      <c r="U22" s="5">
-        <v>36612</v>
-      </c>
-      <c r="V22" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.063013698630137</v>
-      </c>
-      <c r="W22" s="3">
-        <f>5*12+9</f>
-        <v>69</v>
-      </c>
-      <c r="X22" s="3">
-        <v>185</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>10</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>476</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>116.7</v>
-      </c>
-      <c r="AC22" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>11.67</v>
-      </c>
-      <c r="AD22" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.24516806722689077</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="3">
-        <v>10</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E23" s="1">
-        <v>13</v>
-      </c>
-      <c r="F23" s="3">
-        <v>117</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1856</v>
-      </c>
-      <c r="H23" s="3">
-        <v>15.9</v>
-      </c>
-      <c r="I23" s="3">
-        <v>66</v>
-      </c>
-      <c r="J23" s="3">
-        <v>23</v>
-      </c>
-      <c r="K23" s="3">
-        <v>4</v>
-      </c>
-      <c r="L23" s="3">
-        <v>6</v>
-      </c>
-      <c r="M23" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="N23" s="3">
-        <v>1</v>
-      </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
-        <v>36</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>40</v>
-      </c>
-      <c r="R23" s="3">
-        <v>55</v>
-      </c>
-      <c r="S23" s="3">
-        <v>47</v>
-      </c>
-      <c r="T23" s="4">
-        <v>13.3</v>
-      </c>
-      <c r="U23" s="5">
-        <v>36082</v>
-      </c>
-      <c r="V23" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>23.515068493150686</v>
-      </c>
-      <c r="W23" s="3">
-        <f>6*12+1</f>
-        <v>73</v>
-      </c>
-      <c r="X23" s="3">
-        <v>175</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>20.8</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>16</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>916</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>153.6</v>
-      </c>
-      <c r="AC23" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>9.6</v>
-      </c>
-      <c r="AD23" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.16768558951965065</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="3">
-        <v>56</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="1">
-        <v>6</v>
-      </c>
-      <c r="F24" s="3">
-        <v>33</v>
-      </c>
-      <c r="G24" s="3">
-        <v>768</v>
-      </c>
-      <c r="H24" s="3">
-        <v>23.3</v>
-      </c>
-      <c r="I24" s="3">
-        <v>85</v>
-      </c>
-      <c r="J24" s="3">
-        <v>8</v>
-      </c>
-      <c r="K24" s="3">
-        <v>2</v>
-      </c>
-      <c r="L24" s="3">
-        <v>43</v>
-      </c>
-      <c r="M24" s="3">
-        <v>21.5</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>1</v>
-      </c>
-      <c r="P24" s="3">
-        <v>33</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>45</v>
-      </c>
-      <c r="R24" s="3">
-        <v>44</v>
-      </c>
-      <c r="S24" s="3">
-        <v>44</v>
-      </c>
-      <c r="T24" s="4">
-        <v>14.2</v>
-      </c>
-      <c r="U24" s="5">
-        <v>35512</v>
-      </c>
-      <c r="V24" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>25.076712328767123</v>
-      </c>
-      <c r="W24" s="3">
-        <f>5*12+9</f>
-        <v>69</v>
-      </c>
-      <c r="X24" s="3">
-        <v>190</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>20.5</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>2</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>187</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>23.3</v>
-      </c>
-      <c r="AC24" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>11.65</v>
-      </c>
-      <c r="AD24" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.12459893048128343</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="3">
-        <v>129</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" s="1">
-        <v>9</v>
-      </c>
-      <c r="F25" s="3">
-        <v>74</v>
-      </c>
-      <c r="G25" s="3">
-        <v>1190</v>
-      </c>
-      <c r="H25" s="3">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="I25" s="3">
-        <v>75</v>
-      </c>
-      <c r="J25" s="3">
-        <v>19</v>
-      </c>
-      <c r="K25" s="3">
-        <v>2</v>
-      </c>
-      <c r="L25" s="3">
-        <v>-1</v>
-      </c>
-      <c r="M25" s="3">
-        <v>-0.5</v>
-      </c>
-      <c r="N25" s="3">
-        <v>0</v>
-      </c>
-      <c r="O25" s="3">
-        <v>0</v>
-      </c>
-      <c r="P25" s="3">
-        <v>44</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>47</v>
-      </c>
-      <c r="R25" s="3">
-        <v>75</v>
-      </c>
-      <c r="S25" s="3">
-        <v>61</v>
-      </c>
-      <c r="T25" s="4">
-        <v>0</v>
-      </c>
-      <c r="U25" s="5">
-        <v>36174</v>
-      </c>
-      <c r="V25" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>23.263013698630136</v>
-      </c>
-      <c r="W25" s="3">
-        <f>5*12+9</f>
-        <v>69</v>
-      </c>
-      <c r="X25" s="3">
-        <v>174</v>
-      </c>
-      <c r="Y25" s="3">
-        <v>20.6</v>
-      </c>
-      <c r="Z25" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="3">
-        <v>89</v>
-      </c>
-      <c r="AB25" s="3">
-        <v>8.4</v>
-      </c>
-      <c r="AC25" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>8.4</v>
-      </c>
-      <c r="AD25" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>9.4382022471910118E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="3">
-        <v>109</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="1">
-        <v>11</v>
-      </c>
-      <c r="F26" s="3">
-        <v>43</v>
-      </c>
-      <c r="G26" s="3">
-        <v>833</v>
-      </c>
-      <c r="H26" s="3">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="I26" s="3">
-        <v>82</v>
-      </c>
-      <c r="J26" s="3">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1</v>
-      </c>
-      <c r="P26" s="3">
-        <v>21</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>31</v>
-      </c>
-      <c r="R26" s="3">
-        <v>15</v>
-      </c>
-      <c r="S26" s="3">
-        <v>23</v>
-      </c>
-      <c r="T26" s="4">
-        <v>52.6</v>
-      </c>
-      <c r="U26" s="5">
-        <v>35781</v>
-      </c>
-      <c r="V26" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>24.339726027397262</v>
-      </c>
-      <c r="W26" s="3">
-        <f>6*12+2</f>
-        <v>74</v>
-      </c>
-      <c r="X26" s="3">
-        <v>210</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>99</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>13.4</v>
-      </c>
-      <c r="AC26" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>13.4</v>
-      </c>
-      <c r="AD26" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>0.13535353535353536</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="3">
-        <v>82</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E27" s="1">
-        <v>11</v>
-      </c>
-      <c r="F27" s="3">
-        <v>55</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1099</v>
-      </c>
-      <c r="H27" s="3">
-        <v>20</v>
-      </c>
-      <c r="I27" s="3">
-        <v>87</v>
-      </c>
-      <c r="J27" s="3">
-        <v>8</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
-        <v>25</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>33</v>
-      </c>
-      <c r="R27" s="3">
-        <v>28</v>
-      </c>
-      <c r="S27" s="3">
-        <v>30</v>
-      </c>
-      <c r="T27" s="4">
-        <v>11.4</v>
-      </c>
-      <c r="U27" s="5">
-        <v>36465</v>
-      </c>
-      <c r="V27" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.465753424657535</v>
-      </c>
-      <c r="W27" s="3">
-        <f>6*12+1</f>
-        <v>73</v>
-      </c>
-      <c r="X27" s="3">
-        <v>185</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>19.8</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>335</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>22.1</v>
-      </c>
-      <c r="AC27" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>4.42</v>
-      </c>
-      <c r="AD27" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>6.5970149253731347E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3">
-        <v>258</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E28" s="1">
-        <v>12</v>
-      </c>
-      <c r="F28" s="3">
-        <v>70</v>
-      </c>
-      <c r="G28" s="3">
-        <v>1188</v>
-      </c>
-      <c r="H28" s="3">
-        <v>17</v>
-      </c>
-      <c r="I28" s="3">
-        <v>78</v>
-      </c>
-      <c r="J28" s="3">
-        <v>8</v>
-      </c>
-      <c r="K28" s="3">
-        <v>11</v>
-      </c>
-      <c r="L28" s="3">
-        <v>67</v>
-      </c>
-      <c r="M28" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="N28" s="3">
-        <v>0</v>
-      </c>
-      <c r="O28" s="3">
-        <v>2</v>
-      </c>
-      <c r="P28" s="3">
-        <v>26</v>
-      </c>
-      <c r="Q28" s="3">
-        <v>30</v>
-      </c>
-      <c r="R28" s="3">
-        <v>24</v>
-      </c>
-      <c r="S28" s="3">
-        <v>26</v>
-      </c>
-      <c r="T28" s="4">
-        <v>11.4</v>
-      </c>
-      <c r="U28" s="5">
-        <v>36334</v>
-      </c>
-      <c r="V28" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.824657534246576</v>
-      </c>
-      <c r="W28" s="3">
-        <f>6*12</f>
-        <v>72</v>
-      </c>
-      <c r="X28" s="3">
-        <v>190</v>
-      </c>
-      <c r="Y28" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z28" s="3">
-        <v>2</v>
-      </c>
-      <c r="AA28" s="3">
-        <v>163</v>
-      </c>
-      <c r="AB28" s="3">
-        <v>10.9</v>
-      </c>
-      <c r="AC28" s="4">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[NFL.Games]]</f>
-        <v>5.45</v>
-      </c>
-      <c r="AD28" s="12">
-        <f>Table7[[#This Row],[FP]]/Table7[[#This Row],[Snaps]]</f>
-        <v>6.6871165644171782E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="T29" s="4"/>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="T30" s="4"/>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="V30" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD28">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB28">
     <sortCondition ref="C5:C28"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8466,13 +8292,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>40</v>
@@ -8505,22 +8331,22 @@
         <v>13</v>
       </c>
       <c r="P1" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q1" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="R1" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="S1" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="S1" s="11" t="s">
-        <v>142</v>
-      </c>
       <c r="T1" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V1" s="11" t="s">
         <v>14</v>
@@ -8535,24 +8361,24 @@
         <v>44</v>
       </c>
       <c r="Z1" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AA1" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AB1" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC1" s="11" t="s">
         <v>18</v>
       </c>
       <c r="AD1" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>25</v>
@@ -8561,7 +8387,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" s="1">
         <v>8</v>
@@ -8616,7 +8442,7 @@
       </c>
       <c r="V2" s="6">
         <f ca="1">(TODAY()-U2)/365</f>
-        <v>21.534246575342465</v>
+        <v>23.580821917808219</v>
       </c>
       <c r="W2" s="3">
         <f>6*12+6</f>
@@ -8648,16 +8474,16 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" s="3">
         <v>55</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E3" s="1">
         <v>13</v>
@@ -8712,7 +8538,7 @@
       </c>
       <c r="V3" s="6">
         <f t="shared" ref="V3:V8" ca="1" si="0">(TODAY()-U3)/365</f>
-        <v>23.484931506849314</v>
+        <v>25.531506849315068</v>
       </c>
       <c r="W3" s="3">
         <f>6*12+5</f>
@@ -8744,16 +8570,16 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" s="3">
         <v>81</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E4" s="1">
         <v>11</v>
@@ -8808,7 +8634,7 @@
       </c>
       <c r="V4" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>23.668493150684931</v>
+        <v>25.715068493150685</v>
       </c>
       <c r="W4" s="3">
         <f>6*12+5</f>
@@ -8839,7 +8665,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>35</v>
@@ -8848,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E5" s="1">
         <v>12</v>
@@ -8903,7 +8729,7 @@
       </c>
       <c r="V5" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>21.87945205479452</v>
+        <v>23.926027397260274</v>
       </c>
       <c r="W5" s="3">
         <f>6*12+4</f>
@@ -8913,7 +8739,7 @@
         <v>248</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Z5" s="3">
         <v>14</v>
@@ -8935,7 +8761,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -8944,7 +8770,7 @@
         <v>97</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E6" s="1">
         <v>12</v>
@@ -8999,7 +8825,7 @@
       </c>
       <c r="V6" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>23.268493150684932</v>
+        <v>25.315068493150687</v>
       </c>
       <c r="W6" s="3">
         <f>6*12+5</f>
@@ -9009,7 +8835,7 @@
         <v>245</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Z6" s="3">
         <v>3</v>
@@ -9031,16 +8857,16 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="3">
         <v>147</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" s="1">
         <v>8</v>
@@ -9095,7 +8921,7 @@
       </c>
       <c r="V7" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>21.758904109589039</v>
+        <v>23.805479452054794</v>
       </c>
       <c r="W7" s="3">
         <f>6*12+3</f>
@@ -9127,7 +8953,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>67</v>
@@ -9136,7 +8962,7 @@
         <v>162</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E8" s="1">
         <v>10</v>
@@ -9191,7 +9017,7 @@
       </c>
       <c r="V8" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>22.972602739726028</v>
+        <v>25.019178082191782</v>
       </c>
       <c r="W8" s="3">
         <f>6*12+4</f>
